--- a/base_datos.xlsx
+++ b/base_datos.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CAÑERIAS AP" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CAÑERIAS MP" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CAÑERIAS BP" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SERVICIO CAÑERIAS" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONEXIONES" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OBRAS CIVILES" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NORMALIZACIONES" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EQUIPO COMPRA DIRECTA" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SERVICIO COMPRA DIRECTA" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="CAÑERIAS AP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="CAÑERIAS MP" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="CAÑERIAS BP" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="SERVICIO CAÑERIAS" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="CONEXIONES" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="OBRAS CIVILES" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="NORMALIZACIONES" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="EQUIPO COMPRA DIRECTA" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="SERVICIO COMPRA DIRECTA" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CAÑERIAS AP'!$A$1:$G$41</definedName>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="37.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2097,6 +2097,606 @@
       </c>
       <c r="H41" t="n">
         <v>8502</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>LAP10AC 1" (Acero - Alta Presión, material incluido)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>1000099</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CAÑERIAS AP</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Oficina Ventas Copiapó</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>0005</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>16145</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>LAP10AC 1" (Acero - Alta Presión, material incluido)</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>1000099</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>CAÑERIAS AP</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Oficina Ventas Arica</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>0300</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>16145</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>LAP10AC 1" (Acero - Alta Presión, material incluido)</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>1000099</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>CAÑERIAS AP</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Planta Iquique</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>0400</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>16145</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>LAP10AC 1" (Acero - Alta Presión, material incluido)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>1000099</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>CAÑERIAS AP</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Planta Antofagasta</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>0500</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>16145</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>LAP10AC 1" (Acero - Alta Presión, material incluido)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>1000099</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>CAÑERIAS AP</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Oficina Ventas Calama</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>0600</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>16145</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>LAP10AC 3/4" (Acero - Alta Presión, material incluido)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>1000104</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>CAÑERIAS AP</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>3/4</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Oficina Ventas Copiapó</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0005</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>13173</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>LAP10AC 3/4" (Acero - Alta Presión, material incluido)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>1000104</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>CAÑERIAS AP</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>3/4</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Oficina Ventas Arica</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0300</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>13173</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>LAP10AC 3/4" (Acero - Alta Presión, material incluido)</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>1000104</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>CAÑERIAS AP</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>3/4</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Planta Iquique</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0400</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>13173</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>LAP10AC 3/4" (Acero - Alta Presión, material incluido)</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>1000104</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>CAÑERIAS AP</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>3/4</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Planta Antofagasta</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0500</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>13173</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>LAP10AC 3/4" (Acero - Alta Presión, material incluido)</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>1000104</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>CAÑERIAS AP</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>3/4</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Oficina Ventas Calama</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0600</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>13173</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>LAP10AC 1 1/4" (Acero - Alta Presión, material incluido)</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1000098</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>CAÑERIAS AP</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>1 1/4</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Oficina Ventas Copiapó</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0005</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>18826</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>LAP10AC 1 1/4" (Acero - Alta Presión, material incluido)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>1000098</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>CAÑERIAS AP</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1 1/4</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Oficina Ventas Arica</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>0300</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>18826</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>LAP10AC 1 1/4" (Acero - Alta Presión, material incluido)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>1000098</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>CAÑERIAS AP</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>1 1/4</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Planta Iquique</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>0400</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>18826</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>LAP10AC 1 1/4" (Acero - Alta Presión, material incluido)</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>1000098</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>CAÑERIAS AP</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>1 1/4</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Planta Antofagasta</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>0500</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>18826</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>LAP10AC 1 1/4" (Acero - Alta Presión, material incluido)</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>1000098</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>CAÑERIAS AP</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>1 1/4</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Oficina Ventas Calama</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>0600</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>18826</v>
       </c>
     </row>
   </sheetData>

--- a/base_datos.xlsx
+++ b/base_datos.xlsx
@@ -9141,7 +9141,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>3000</v>
+        <v>3248</v>
       </c>
     </row>
     <row r="3">
@@ -9176,7 +9176,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>15000</v>
+        <v>16238</v>
       </c>
     </row>
     <row r="4">
@@ -9211,7 +9211,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1150</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="5">
@@ -9246,7 +9246,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1617</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="6">
@@ -9281,7 +9281,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>3000</v>
+        <v>3124</v>
       </c>
     </row>
     <row r="7">
@@ -9316,7 +9316,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>15000</v>
+        <v>15619</v>
       </c>
     </row>
     <row r="8">
@@ -9351,7 +9351,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>15000</v>
+        <v>13761</v>
       </c>
     </row>
     <row r="9">
@@ -9386,7 +9386,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>20000</v>
+        <v>18348</v>
       </c>
     </row>
     <row r="10">
@@ -9421,7 +9421,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1500</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="11">
@@ -9456,7 +9456,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1500</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="12">
@@ -9491,7 +9491,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1150</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="13">
@@ -9526,7 +9526,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>2450</v>
+        <v>2248</v>
       </c>
     </row>
     <row r="14">
@@ -9561,7 +9561,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1617</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="15">
@@ -9596,7 +9596,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1188</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="16">
@@ -9631,7 +9631,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>15000</v>
+        <v>14380</v>
       </c>
     </row>
     <row r="17">
@@ -9666,7 +9666,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1500</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="18">
@@ -9701,7 +9701,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1500</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="19">
@@ -9736,7 +9736,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1150</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="20">
@@ -9771,7 +9771,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>2450</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="21">
@@ -9806,7 +9806,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1617</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="22">
@@ -9876,7 +9876,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>3000</v>
+        <v>2876</v>
       </c>
     </row>
     <row r="24">
@@ -9911,7 +9911,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>3000</v>
+        <v>2752</v>
       </c>
     </row>
     <row r="25">
@@ -10016,7 +10016,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1150</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="28">
@@ -10086,7 +10086,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1617</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="30">
@@ -10156,7 +10156,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>20000</v>
+        <v>20826</v>
       </c>
     </row>
     <row r="32">
@@ -10191,7 +10191,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>20000</v>
+        <v>21650</v>
       </c>
     </row>
     <row r="33">
@@ -10226,7 +10226,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>20000</v>
+        <v>19174</v>
       </c>
     </row>
     <row r="34">
@@ -10296,7 +10296,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>1500</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="36">
@@ -10331,7 +10331,7 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>1500</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="37">
@@ -10401,7 +10401,7 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>1500</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="39">
@@ -10436,7 +10436,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>1500</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="40">
@@ -10506,7 +10506,7 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>2450</v>
+        <v>2551</v>
       </c>
     </row>
     <row r="42">
@@ -10541,7 +10541,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>2450</v>
+        <v>2652</v>
       </c>
     </row>
     <row r="43">
@@ -10611,7 +10611,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>1188</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="45">
@@ -10646,7 +10646,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>1188</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="46">
@@ -10681,7 +10681,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>1188</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="47">
@@ -10716,7 +10716,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>2150</v>
+        <v>2327</v>
       </c>
     </row>
     <row r="48">
@@ -10751,7 +10751,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>2150</v>
+        <v>2239</v>
       </c>
     </row>
     <row r="49">
@@ -10786,7 +10786,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>2150</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="50">
@@ -10821,7 +10821,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>2150</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="51">
@@ -10945,7 +10945,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>37000</v>
+        <v>40052</v>
       </c>
     </row>
     <row r="3">
@@ -10980,7 +10980,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>16894</v>
+        <v>24009</v>
       </c>
     </row>
     <row r="4">
@@ -11015,7 +11015,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>27500</v>
+        <v>29769</v>
       </c>
     </row>
     <row r="5">
@@ -11050,7 +11050,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>26084</v>
+        <v>29462</v>
       </c>
     </row>
     <row r="6">
@@ -11085,7 +11085,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>45000</v>
+        <v>48712</v>
       </c>
     </row>
     <row r="7">
@@ -11120,7 +11120,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>38500</v>
+        <v>41676</v>
       </c>
     </row>
     <row r="8">
@@ -11155,7 +11155,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>28775</v>
+        <v>39138</v>
       </c>
     </row>
     <row r="9">
@@ -11190,7 +11190,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>25000</v>
+        <v>27062</v>
       </c>
     </row>
     <row r="10">
@@ -11225,7 +11225,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>14950</v>
+        <v>19691</v>
       </c>
     </row>
     <row r="11">
@@ -11260,7 +11260,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>8958</v>
+        <v>10599</v>
       </c>
     </row>
     <row r="12">
@@ -11295,7 +11295,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>5556</v>
+        <v>6014</v>
       </c>
     </row>
     <row r="13">
@@ -11330,7 +11330,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>21000</v>
+        <v>22732</v>
       </c>
     </row>
     <row r="14">
@@ -11365,7 +11365,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>39980</v>
+        <v>43278</v>
       </c>
     </row>
     <row r="15">
@@ -11400,7 +11400,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>67935</v>
+        <v>73540</v>
       </c>
     </row>
     <row r="16">
@@ -11435,7 +11435,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>20000</v>
+        <v>21650</v>
       </c>
     </row>
     <row r="17">
@@ -11470,7 +11470,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>2752</v>
+        <v>2979</v>
       </c>
     </row>
     <row r="18">
@@ -11505,7 +11505,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>11954</v>
+        <v>12940</v>
       </c>
     </row>
     <row r="19">
@@ -11540,7 +11540,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
     </row>
     <row r="20">
@@ -11575,7 +11575,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>37000</v>
+        <v>38528</v>
       </c>
     </row>
     <row r="21">
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>25000</v>
+        <v>26032</v>
       </c>
     </row>
     <row r="22">
@@ -11645,7 +11645,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>25000</v>
+        <v>26032</v>
       </c>
     </row>
     <row r="23">
@@ -11680,7 +11680,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>25000</v>
+        <v>26032</v>
       </c>
     </row>
     <row r="24">
@@ -11715,7 +11715,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>25000</v>
+        <v>26032</v>
       </c>
     </row>
     <row r="25">
@@ -11750,7 +11750,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>25000</v>
+        <v>26032</v>
       </c>
     </row>
     <row r="26">
@@ -11785,7 +11785,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>27500</v>
+        <v>28341</v>
       </c>
     </row>
     <row r="27">
@@ -11820,7 +11820,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>25000</v>
+        <v>26032</v>
       </c>
     </row>
     <row r="28">
@@ -11855,7 +11855,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>45000</v>
+        <v>46858</v>
       </c>
     </row>
     <row r="29">
@@ -11890,7 +11890,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>38500</v>
+        <v>40090</v>
       </c>
     </row>
     <row r="30">
@@ -11925,7 +11925,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>38000</v>
+        <v>37648</v>
       </c>
     </row>
     <row r="31">
@@ -11960,7 +11960,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>25000</v>
+        <v>26032</v>
       </c>
     </row>
     <row r="32">
@@ -11995,7 +11995,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>19000</v>
+        <v>18941</v>
       </c>
     </row>
     <row r="33">
@@ -12030,7 +12030,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>37000</v>
+        <v>33944</v>
       </c>
     </row>
     <row r="34">
@@ -12065,7 +12065,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>20750</v>
+        <v>19036</v>
       </c>
     </row>
     <row r="35">
@@ -12100,7 +12100,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>25000</v>
+        <v>22935</v>
       </c>
     </row>
     <row r="36">
@@ -12135,7 +12135,7 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>2880</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="37">
@@ -12170,7 +12170,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>23500</v>
+        <v>20347</v>
       </c>
     </row>
     <row r="38">
@@ -12205,7 +12205,7 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>33000</v>
+        <v>30274</v>
       </c>
     </row>
     <row r="39">
@@ -12240,7 +12240,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>25000</v>
+        <v>22935</v>
       </c>
     </row>
     <row r="40">
@@ -12275,7 +12275,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>27500</v>
+        <v>25228</v>
       </c>
     </row>
     <row r="41">
@@ -12310,7 +12310,7 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>25000</v>
+        <v>22935</v>
       </c>
     </row>
     <row r="42">
@@ -12345,7 +12345,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>27500</v>
+        <v>24969</v>
       </c>
     </row>
     <row r="43">
@@ -12380,7 +12380,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>25000</v>
+        <v>22935</v>
       </c>
     </row>
     <row r="44">
@@ -12415,7 +12415,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>45000</v>
+        <v>41283</v>
       </c>
     </row>
     <row r="45">
@@ -12450,7 +12450,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>38500</v>
+        <v>35320</v>
       </c>
     </row>
     <row r="46">
@@ -12485,7 +12485,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>41800</v>
+        <v>38347</v>
       </c>
     </row>
     <row r="47">
@@ -12520,7 +12520,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>38000</v>
+        <v>33169</v>
       </c>
     </row>
     <row r="48">
@@ -12555,7 +12555,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>25000</v>
+        <v>22935</v>
       </c>
     </row>
     <row r="49">
@@ -12590,7 +12590,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>19000</v>
+        <v>16688</v>
       </c>
     </row>
     <row r="50">
@@ -12625,7 +12625,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>10000</v>
+        <v>8983</v>
       </c>
     </row>
     <row r="51">
@@ -12660,7 +12660,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>5556</v>
+        <v>5097</v>
       </c>
     </row>
     <row r="52">
@@ -12695,7 +12695,7 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>20000</v>
+        <v>18348</v>
       </c>
     </row>
     <row r="53">
@@ -12730,7 +12730,7 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>21000</v>
+        <v>19265</v>
       </c>
     </row>
     <row r="54">
@@ -12765,7 +12765,7 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>67935</v>
+        <v>62324</v>
       </c>
     </row>
     <row r="55">
@@ -12800,7 +12800,7 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>64878</v>
+        <v>59519</v>
       </c>
     </row>
     <row r="56">
@@ -12835,7 +12835,7 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>107028</v>
+        <v>98187</v>
       </c>
     </row>
     <row r="57">
@@ -12870,7 +12870,7 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>138869</v>
+        <v>127398</v>
       </c>
     </row>
     <row r="58">
@@ -12905,7 +12905,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>20000</v>
+        <v>18348</v>
       </c>
     </row>
     <row r="59">
@@ -12940,7 +12940,7 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>37000</v>
+        <v>35472</v>
       </c>
     </row>
     <row r="60">
@@ -12975,7 +12975,7 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>25000</v>
+        <v>23968</v>
       </c>
     </row>
     <row r="61">
@@ -13010,7 +13010,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>23500</v>
+        <v>21263</v>
       </c>
     </row>
     <row r="62">
@@ -13045,7 +13045,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>27500</v>
+        <v>26364</v>
       </c>
     </row>
     <row r="63">
@@ -13080,7 +13080,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>27500</v>
+        <v>26093</v>
       </c>
     </row>
     <row r="64">
@@ -13115,7 +13115,7 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>45000</v>
+        <v>43142</v>
       </c>
     </row>
     <row r="65">
@@ -13150,7 +13150,7 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>38500</v>
+        <v>36910</v>
       </c>
     </row>
     <row r="66">
@@ -13185,7 +13185,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>38000</v>
+        <v>34662</v>
       </c>
     </row>
     <row r="67">
@@ -13220,7 +13220,7 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>25000</v>
+        <v>23968</v>
       </c>
     </row>
     <row r="68">
@@ -13255,7 +13255,7 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>19000</v>
+        <v>17439</v>
       </c>
     </row>
     <row r="69">
@@ -13290,7 +13290,7 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>10000</v>
+        <v>9387</v>
       </c>
     </row>
     <row r="70">
@@ -13325,7 +13325,7 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>5556</v>
+        <v>5327</v>
       </c>
     </row>
     <row r="71">
@@ -13360,7 +13360,7 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>21000</v>
+        <v>20133</v>
       </c>
     </row>
     <row r="72">
@@ -13395,7 +13395,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>134565</v>
+        <v>129007</v>
       </c>
     </row>
     <row r="73">
@@ -13430,7 +13430,7 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>138869</v>
+        <v>133134</v>
       </c>
     </row>
     <row r="74">
@@ -13465,7 +13465,7 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>20000</v>
+        <v>19174</v>
       </c>
     </row>
     <row r="75">
@@ -13500,7 +13500,7 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>54955</v>
+        <v>59489</v>
       </c>
     </row>
     <row r="76">
@@ -13535,7 +13535,7 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>54955</v>
+        <v>57225</v>
       </c>
     </row>
     <row r="77">
@@ -13570,7 +13570,7 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>54955</v>
+        <v>52685</v>
       </c>
     </row>
     <row r="78">
@@ -13605,7 +13605,7 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>54955</v>
+        <v>50416</v>
       </c>
     </row>
     <row r="79">
@@ -13675,7 +13675,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>85461</v>
+        <v>92512</v>
       </c>
     </row>
     <row r="81">
@@ -13710,7 +13710,7 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>85461</v>
+        <v>88991</v>
       </c>
     </row>
     <row r="82">
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>85461</v>
+        <v>81931</v>
       </c>
     </row>
     <row r="83">
@@ -13780,7 +13780,7 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>85461</v>
+        <v>78402</v>
       </c>
     </row>
     <row r="84">
@@ -13850,7 +13850,7 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>173373</v>
+        <v>187676</v>
       </c>
     </row>
     <row r="86">
@@ -13885,7 +13885,7 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>173373</v>
+        <v>180533</v>
       </c>
     </row>
     <row r="87">
@@ -13920,7 +13920,7 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>173373</v>
+        <v>166213</v>
       </c>
     </row>
     <row r="88">
@@ -13955,7 +13955,7 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>173373</v>
+        <v>159052</v>
       </c>
     </row>
     <row r="89">
@@ -14025,7 +14025,7 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>50000</v>
+        <v>54125</v>
       </c>
     </row>
     <row r="91">
@@ -14060,7 +14060,7 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>50000</v>
+        <v>52065</v>
       </c>
     </row>
     <row r="92">
@@ -14095,7 +14095,7 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>50000</v>
+        <v>47935</v>
       </c>
     </row>
     <row r="93">
@@ -14130,7 +14130,7 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>50000</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="94">
@@ -14200,7 +14200,7 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>38000</v>
+        <v>41135</v>
       </c>
     </row>
     <row r="96">
@@ -14235,7 +14235,7 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>38000</v>
+        <v>39569</v>
       </c>
     </row>
     <row r="97">
@@ -14270,7 +14270,7 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>38000</v>
+        <v>36431</v>
       </c>
     </row>
     <row r="98">
@@ -14305,7 +14305,7 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>38000</v>
+        <v>34861</v>
       </c>
     </row>
     <row r="99">
@@ -14375,7 +14375,7 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>38000</v>
+        <v>41135</v>
       </c>
     </row>
     <row r="101">
@@ -14410,7 +14410,7 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>38000</v>
+        <v>39569</v>
       </c>
     </row>
     <row r="102">
@@ -14445,7 +14445,7 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>38000</v>
+        <v>36431</v>
       </c>
     </row>
     <row r="103">
@@ -14480,7 +14480,7 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>38000</v>
+        <v>34861</v>
       </c>
     </row>
     <row r="104">
@@ -14550,7 +14550,7 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>42000</v>
+        <v>45465</v>
       </c>
     </row>
     <row r="106">
@@ -14585,7 +14585,7 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>42000</v>
+        <v>43735</v>
       </c>
     </row>
     <row r="107">
@@ -14620,7 +14620,7 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>42000</v>
+        <v>40265</v>
       </c>
     </row>
     <row r="108">
@@ -14655,7 +14655,7 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>42000</v>
+        <v>38531</v>
       </c>
     </row>
     <row r="109">
@@ -14725,7 +14725,7 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>15000</v>
+        <v>16238</v>
       </c>
     </row>
     <row r="111">
@@ -14760,7 +14760,7 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>15000</v>
+        <v>15619</v>
       </c>
     </row>
     <row r="112">
@@ -14795,7 +14795,7 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>15000</v>
+        <v>14380</v>
       </c>
     </row>
     <row r="113">
@@ -14830,7 +14830,7 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>15000</v>
+        <v>13761</v>
       </c>
     </row>
     <row r="114">
@@ -14900,7 +14900,7 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>350000</v>
+        <v>378875</v>
       </c>
     </row>
     <row r="116">
@@ -14935,7 +14935,7 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>350000</v>
+        <v>364455</v>
       </c>
     </row>
     <row r="117">
@@ -14970,7 +14970,7 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>350000</v>
+        <v>335545</v>
       </c>
     </row>
     <row r="118">
@@ -15005,7 +15005,7 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>350000</v>
+        <v>321090</v>
       </c>
     </row>
     <row r="119">
@@ -15075,7 +15075,7 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>75000</v>
+        <v>81188</v>
       </c>
     </row>
     <row r="121">
@@ -15110,7 +15110,7 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>75000</v>
+        <v>78097</v>
       </c>
     </row>
     <row r="122">
@@ -15145,7 +15145,7 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>75000</v>
+        <v>71902</v>
       </c>
     </row>
     <row r="123">
@@ -15180,7 +15180,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>75000</v>
+        <v>68805</v>
       </c>
     </row>
     <row r="124">
@@ -15250,7 +15250,7 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>32000</v>
+        <v>34640</v>
       </c>
     </row>
     <row r="126">
@@ -15285,7 +15285,7 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>32000</v>
+        <v>33322</v>
       </c>
     </row>
     <row r="127">
@@ -15320,7 +15320,7 @@
         </is>
       </c>
       <c r="G127" t="n">
-        <v>32000</v>
+        <v>30678</v>
       </c>
     </row>
     <row r="128">
@@ -15355,7 +15355,7 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>32000</v>
+        <v>29357</v>
       </c>
     </row>
     <row r="129">
@@ -15425,7 +15425,7 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>12000</v>
+        <v>12990</v>
       </c>
     </row>
     <row r="131">
@@ -15460,7 +15460,7 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>12000</v>
+        <v>12496</v>
       </c>
     </row>
     <row r="132">
@@ -15495,7 +15495,7 @@
         </is>
       </c>
       <c r="G132" t="n">
-        <v>12000</v>
+        <v>11504</v>
       </c>
     </row>
     <row r="133">
@@ -15530,7 +15530,7 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>12000</v>
+        <v>11009</v>
       </c>
     </row>
     <row r="134">
@@ -15600,7 +15600,7 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>20213</v>
+        <v>21881</v>
       </c>
     </row>
     <row r="136">
@@ -15635,7 +15635,7 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>20213</v>
+        <v>21048</v>
       </c>
     </row>
     <row r="137">
@@ -15670,7 +15670,7 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>20213</v>
+        <v>19378</v>
       </c>
     </row>
     <row r="138">
@@ -15705,7 +15705,7 @@
         </is>
       </c>
       <c r="G138" t="n">
-        <v>20213</v>
+        <v>18543</v>
       </c>
     </row>
     <row r="139">
@@ -15775,7 +15775,7 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>50000</v>
+        <v>54125</v>
       </c>
     </row>
     <row r="141">
@@ -15810,7 +15810,7 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>50000</v>
+        <v>52065</v>
       </c>
     </row>
     <row r="142">
@@ -15845,7 +15845,7 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>50000</v>
+        <v>47935</v>
       </c>
     </row>
     <row r="143">
@@ -15880,7 +15880,7 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>50000</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="144">
@@ -15950,7 +15950,7 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>7000</v>
+        <v>7578</v>
       </c>
     </row>
     <row r="146">
@@ -15985,7 +15985,7 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>7000</v>
+        <v>7289</v>
       </c>
     </row>
     <row r="147">
@@ -16020,7 +16020,7 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>7000</v>
+        <v>6711</v>
       </c>
     </row>
     <row r="148">
@@ -16055,7 +16055,7 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>7000</v>
+        <v>6422</v>
       </c>
     </row>
     <row r="149">
@@ -16160,7 +16160,7 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>23500</v>
+        <v>22179</v>
       </c>
     </row>
     <row r="152">
@@ -16195,7 +16195,7 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>23500</v>
+        <v>23095</v>
       </c>
     </row>
     <row r="153">
@@ -16265,7 +16265,7 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>27500</v>
+        <v>28636</v>
       </c>
     </row>
     <row r="155">
@@ -16300,7 +16300,7 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>27500</v>
+        <v>27217</v>
       </c>
     </row>
     <row r="156">
@@ -16405,7 +16405,7 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>38000</v>
+        <v>36155</v>
       </c>
     </row>
     <row r="159">
@@ -16475,7 +16475,7 @@
         </is>
       </c>
       <c r="G160" t="n">
-        <v>19000</v>
+        <v>18190</v>
       </c>
     </row>
     <row r="161">
@@ -16510,7 +16510,7 @@
         </is>
       </c>
       <c r="G161" t="n">
-        <v>10000</v>
+        <v>9792</v>
       </c>
     </row>
     <row r="162">
@@ -16545,7 +16545,7 @@
         </is>
       </c>
       <c r="G162" t="n">
-        <v>10000</v>
+        <v>10196</v>
       </c>
     </row>
     <row r="163">
@@ -16615,7 +16615,7 @@
         </is>
       </c>
       <c r="G164" t="n">
-        <v>5556</v>
+        <v>5785</v>
       </c>
     </row>
     <row r="165">
@@ -16685,7 +16685,7 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>21000</v>
+        <v>21867</v>
       </c>
     </row>
     <row r="167">
@@ -16755,7 +16755,7 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>39980</v>
+        <v>41631</v>
       </c>
     </row>
     <row r="169">
@@ -16790,7 +16790,7 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>39980</v>
+        <v>38329</v>
       </c>
     </row>
     <row r="170">
@@ -16825,7 +16825,7 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>39980</v>
+        <v>36678</v>
       </c>
     </row>
     <row r="171">
@@ -16895,7 +16895,7 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>67935</v>
+        <v>70741</v>
       </c>
     </row>
     <row r="173">
@@ -16930,7 +16930,7 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>67935</v>
+        <v>65129</v>
       </c>
     </row>
     <row r="174">
@@ -17000,7 +17000,7 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>20000</v>
+        <v>20826</v>
       </c>
     </row>
     <row r="176">
@@ -17070,7 +17070,7 @@
         </is>
       </c>
       <c r="G177" t="n">
-        <v>2752</v>
+        <v>2866</v>
       </c>
     </row>
     <row r="178">
@@ -17105,7 +17105,7 @@
         </is>
       </c>
       <c r="G178" t="n">
-        <v>2752</v>
+        <v>2638</v>
       </c>
     </row>
     <row r="179">
@@ -17140,7 +17140,7 @@
         </is>
       </c>
       <c r="G179" t="n">
-        <v>2752</v>
+        <v>2525</v>
       </c>
     </row>
     <row r="180">
@@ -17210,7 +17210,7 @@
         </is>
       </c>
       <c r="G181" t="n">
-        <v>11954</v>
+        <v>12448</v>
       </c>
     </row>
     <row r="182">
@@ -17245,7 +17245,7 @@
         </is>
       </c>
       <c r="G182" t="n">
-        <v>11954</v>
+        <v>11460</v>
       </c>
     </row>
     <row r="183">
@@ -17280,7 +17280,7 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>11954</v>
+        <v>10967</v>
       </c>
     </row>
     <row r="184">
@@ -17350,7 +17350,7 @@
         </is>
       </c>
       <c r="G185" t="n">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="186">
@@ -17385,7 +17385,7 @@
         </is>
       </c>
       <c r="G186" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
     </row>
     <row r="187">
@@ -17420,7 +17420,7 @@
         </is>
       </c>
       <c r="G187" t="n">
-        <v>113</v>
+        <v>104</v>
       </c>
     </row>
     <row r="188">
@@ -17490,7 +17490,7 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>25000</v>
+        <v>23968</v>
       </c>
     </row>
     <row r="190">
@@ -17525,7 +17525,7 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>25000</v>
+        <v>27062</v>
       </c>
     </row>
     <row r="191">
@@ -17560,7 +17560,7 @@
         </is>
       </c>
       <c r="G191" t="n">
-        <v>25000</v>
+        <v>22935</v>
       </c>
     </row>
     <row r="192">
@@ -17630,7 +17630,7 @@
         </is>
       </c>
       <c r="G193" t="n">
-        <v>25000</v>
+        <v>27062</v>
       </c>
     </row>
     <row r="194">
@@ -17665,7 +17665,7 @@
         </is>
       </c>
       <c r="G194" t="n">
-        <v>25000</v>
+        <v>22935</v>
       </c>
     </row>
     <row r="195">
@@ -17735,7 +17735,7 @@
         </is>
       </c>
       <c r="G196" t="n">
-        <v>25000</v>
+        <v>23968</v>
       </c>
     </row>
     <row r="197">
@@ -17770,7 +17770,7 @@
         </is>
       </c>
       <c r="G197" t="n">
-        <v>25000</v>
+        <v>27062</v>
       </c>
     </row>
     <row r="198">
@@ -17805,7 +17805,7 @@
         </is>
       </c>
       <c r="G198" t="n">
-        <v>25000</v>
+        <v>22935</v>
       </c>
     </row>
     <row r="199">
@@ -17875,7 +17875,7 @@
         </is>
       </c>
       <c r="G200" t="n">
-        <v>25000</v>
+        <v>23968</v>
       </c>
     </row>
     <row r="201">
@@ -17910,7 +17910,7 @@
         </is>
       </c>
       <c r="G201" t="n">
-        <v>25000</v>
+        <v>27062</v>
       </c>
     </row>
     <row r="202">
@@ -17980,7 +17980,7 @@
         </is>
       </c>
       <c r="G203" t="n">
-        <v>25000</v>
+        <v>23968</v>
       </c>
     </row>
     <row r="204">
@@ -18015,7 +18015,7 @@
         </is>
       </c>
       <c r="G204" t="n">
-        <v>25000</v>
+        <v>27062</v>
       </c>
     </row>
     <row r="205">
@@ -18085,7 +18085,7 @@
         </is>
       </c>
       <c r="G206" t="n">
-        <v>25000</v>
+        <v>23968</v>
       </c>
     </row>
     <row r="207">
@@ -18120,7 +18120,7 @@
         </is>
       </c>
       <c r="G207" t="n">
-        <v>25000</v>
+        <v>27062</v>
       </c>
     </row>
     <row r="208">
@@ -18190,7 +18190,7 @@
         </is>
       </c>
       <c r="G209" t="n">
-        <v>20750</v>
+        <v>21607</v>
       </c>
     </row>
     <row r="210">
@@ -18225,7 +18225,7 @@
         </is>
       </c>
       <c r="G210" t="n">
-        <v>20750</v>
+        <v>22462</v>
       </c>
     </row>
     <row r="211">
@@ -18260,7 +18260,7 @@
         </is>
       </c>
       <c r="G211" t="n">
-        <v>20750</v>
+        <v>19893</v>
       </c>
     </row>
     <row r="212">
@@ -18330,7 +18330,7 @@
         </is>
       </c>
       <c r="G213" t="n">
-        <v>2880</v>
+        <v>2999</v>
       </c>
     </row>
     <row r="214">
@@ -18365,7 +18365,7 @@
         </is>
       </c>
       <c r="G214" t="n">
-        <v>2880</v>
+        <v>3118</v>
       </c>
     </row>
     <row r="215">
@@ -18400,7 +18400,7 @@
         </is>
       </c>
       <c r="G215" t="n">
-        <v>2880</v>
+        <v>2761</v>
       </c>
     </row>
     <row r="216">
@@ -18470,7 +18470,7 @@
         </is>
       </c>
       <c r="G217" t="n">
-        <v>33000</v>
+        <v>34363</v>
       </c>
     </row>
     <row r="218">
@@ -18505,7 +18505,7 @@
         </is>
       </c>
       <c r="G218" t="n">
-        <v>33000</v>
+        <v>35722</v>
       </c>
     </row>
     <row r="219">
@@ -18540,7 +18540,7 @@
         </is>
       </c>
       <c r="G219" t="n">
-        <v>33000</v>
+        <v>31637</v>
       </c>
     </row>
     <row r="220">
@@ -18610,7 +18610,7 @@
         </is>
       </c>
       <c r="G221" t="n">
-        <v>25000</v>
+        <v>26032</v>
       </c>
     </row>
     <row r="222">
@@ -18645,7 +18645,7 @@
         </is>
       </c>
       <c r="G222" t="n">
-        <v>25000</v>
+        <v>27062</v>
       </c>
     </row>
     <row r="223">
@@ -18680,7 +18680,7 @@
         </is>
       </c>
       <c r="G223" t="n">
-        <v>25000</v>
+        <v>23968</v>
       </c>
     </row>
     <row r="224">
@@ -18750,7 +18750,7 @@
         </is>
       </c>
       <c r="G225" t="n">
-        <v>41800</v>
+        <v>43526</v>
       </c>
     </row>
     <row r="226">
@@ -18785,7 +18785,7 @@
         </is>
       </c>
       <c r="G226" t="n">
-        <v>41800</v>
+        <v>45248</v>
       </c>
     </row>
     <row r="227">
@@ -18820,7 +18820,7 @@
         </is>
       </c>
       <c r="G227" t="n">
-        <v>41800</v>
+        <v>40074</v>
       </c>
     </row>
     <row r="228">
@@ -18890,7 +18890,7 @@
         </is>
       </c>
       <c r="G229" t="n">
-        <v>20000</v>
+        <v>20826</v>
       </c>
     </row>
     <row r="230">
@@ -18925,7 +18925,7 @@
         </is>
       </c>
       <c r="G230" t="n">
-        <v>20000</v>
+        <v>21650</v>
       </c>
     </row>
     <row r="231">
@@ -18960,7 +18960,7 @@
         </is>
       </c>
       <c r="G231" t="n">
-        <v>20000</v>
+        <v>19174</v>
       </c>
     </row>
     <row r="232">
@@ -19030,7 +19030,7 @@
         </is>
       </c>
       <c r="G233" t="n">
-        <v>64878</v>
+        <v>67557</v>
       </c>
     </row>
     <row r="234">
@@ -19065,7 +19065,7 @@
         </is>
       </c>
       <c r="G234" t="n">
-        <v>64878</v>
+        <v>70230</v>
       </c>
     </row>
     <row r="235">
@@ -19100,7 +19100,7 @@
         </is>
       </c>
       <c r="G235" t="n">
-        <v>64878</v>
+        <v>62199</v>
       </c>
     </row>
     <row r="236">
@@ -19170,7 +19170,7 @@
         </is>
       </c>
       <c r="G237" t="n">
-        <v>107028</v>
+        <v>111448</v>
       </c>
     </row>
     <row r="238">
@@ -19205,7 +19205,7 @@
         </is>
       </c>
       <c r="G238" t="n">
-        <v>107028</v>
+        <v>115858</v>
       </c>
     </row>
     <row r="239">
@@ -19240,7 +19240,7 @@
         </is>
       </c>
       <c r="G239" t="n">
-        <v>107028</v>
+        <v>102608</v>
       </c>
     </row>
     <row r="240">
@@ -19310,7 +19310,7 @@
         </is>
       </c>
       <c r="G241" t="n">
-        <v>138869</v>
+        <v>144604</v>
       </c>
     </row>
     <row r="242">
@@ -19345,7 +19345,7 @@
         </is>
       </c>
       <c r="G242" t="n">
-        <v>138869</v>
+        <v>150326</v>
       </c>
     </row>
     <row r="243">
@@ -19415,7 +19415,7 @@
         </is>
       </c>
       <c r="G244" t="n">
-        <v>134565</v>
+        <v>140123</v>
       </c>
     </row>
     <row r="245">
@@ -19450,7 +19450,7 @@
         </is>
       </c>
       <c r="G245" t="n">
-        <v>134565</v>
+        <v>145667</v>
       </c>
     </row>
     <row r="246">
@@ -19485,7 +19485,7 @@
         </is>
       </c>
       <c r="G246" t="n">
-        <v>134565</v>
+        <v>123450</v>
       </c>
     </row>
     <row r="247">
@@ -19520,7 +19520,7 @@
         </is>
       </c>
       <c r="G247" t="n">
-        <v>55562</v>
+        <v>60146</v>
       </c>
     </row>
     <row r="248">
@@ -19555,7 +19555,7 @@
         </is>
       </c>
       <c r="G248" t="n">
-        <v>55562</v>
+        <v>57857</v>
       </c>
     </row>
     <row r="249">
@@ -19590,7 +19590,7 @@
         </is>
       </c>
       <c r="G249" t="n">
-        <v>55562</v>
+        <v>53267</v>
       </c>
     </row>
     <row r="250">
@@ -19625,7 +19625,7 @@
         </is>
       </c>
       <c r="G250" t="n">
-        <v>55562</v>
+        <v>50973</v>
       </c>
     </row>
     <row r="251">
@@ -19695,7 +19695,7 @@
         </is>
       </c>
       <c r="G252" t="n">
-        <v>38500</v>
+        <v>41676</v>
       </c>
     </row>
     <row r="253">
@@ -19730,7 +19730,7 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>38500</v>
+        <v>40090</v>
       </c>
     </row>
     <row r="254">
@@ -19765,7 +19765,7 @@
         </is>
       </c>
       <c r="G254" t="n">
-        <v>38500</v>
+        <v>36910</v>
       </c>
     </row>
     <row r="255">
@@ -19800,7 +19800,7 @@
         </is>
       </c>
       <c r="G255" t="n">
-        <v>38500</v>
+        <v>35320</v>
       </c>
     </row>
     <row r="256">
@@ -19870,7 +19870,7 @@
         </is>
       </c>
       <c r="G257" t="n">
-        <v>25000</v>
+        <v>27062</v>
       </c>
     </row>
     <row r="258">
@@ -19905,7 +19905,7 @@
         </is>
       </c>
       <c r="G258" t="n">
-        <v>25000</v>
+        <v>26032</v>
       </c>
     </row>
     <row r="259">
@@ -19940,7 +19940,7 @@
         </is>
       </c>
       <c r="G259" t="n">
-        <v>25000</v>
+        <v>23968</v>
       </c>
     </row>
     <row r="260">
@@ -19975,7 +19975,7 @@
         </is>
       </c>
       <c r="G260" t="n">
-        <v>25000</v>
+        <v>22935</v>
       </c>
     </row>
     <row r="261">
@@ -20045,7 +20045,7 @@
         </is>
       </c>
       <c r="G262" t="n">
-        <v>25000</v>
+        <v>27062</v>
       </c>
     </row>
     <row r="263">
@@ -20080,7 +20080,7 @@
         </is>
       </c>
       <c r="G263" t="n">
-        <v>25000</v>
+        <v>26032</v>
       </c>
     </row>
     <row r="264">
@@ -20115,7 +20115,7 @@
         </is>
       </c>
       <c r="G264" t="n">
-        <v>25000</v>
+        <v>23968</v>
       </c>
     </row>
     <row r="265">
@@ -20150,7 +20150,7 @@
         </is>
       </c>
       <c r="G265" t="n">
-        <v>25000</v>
+        <v>22935</v>
       </c>
     </row>
     <row r="266">
@@ -20220,7 +20220,7 @@
         </is>
       </c>
       <c r="G267" t="n">
-        <v>30000</v>
+        <v>32475</v>
       </c>
     </row>
     <row r="268">
@@ -20255,7 +20255,7 @@
         </is>
       </c>
       <c r="G268" t="n">
-        <v>30000</v>
+        <v>31239</v>
       </c>
     </row>
     <row r="269">
@@ -20290,7 +20290,7 @@
         </is>
       </c>
       <c r="G269" t="n">
-        <v>30000</v>
+        <v>28761</v>
       </c>
     </row>
     <row r="270">
@@ -20325,7 +20325,7 @@
         </is>
       </c>
       <c r="G270" t="n">
-        <v>30000</v>
+        <v>27522</v>
       </c>
     </row>
     <row r="271">
@@ -20395,7 +20395,7 @@
         </is>
       </c>
       <c r="G272" t="n">
-        <v>38000</v>
+        <v>41135</v>
       </c>
     </row>
     <row r="273">
@@ -20430,7 +20430,7 @@
         </is>
       </c>
       <c r="G273" t="n">
-        <v>38000</v>
+        <v>39569</v>
       </c>
     </row>
     <row r="274">
@@ -20465,7 +20465,7 @@
         </is>
       </c>
       <c r="G274" t="n">
-        <v>38000</v>
+        <v>36431</v>
       </c>
     </row>
     <row r="275">
@@ -20500,7 +20500,7 @@
         </is>
       </c>
       <c r="G275" t="n">
-        <v>38000</v>
+        <v>34861</v>
       </c>
     </row>
     <row r="276">
@@ -20624,7 +20624,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>12979</v>
+        <v>15137</v>
       </c>
     </row>
     <row r="3">
@@ -20659,7 +20659,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>39452</v>
+        <v>42825</v>
       </c>
     </row>
     <row r="4">
@@ -20694,7 +20694,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>44162</v>
+        <v>64224</v>
       </c>
     </row>
     <row r="5">
@@ -20729,7 +20729,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>42750</v>
+        <v>46277</v>
       </c>
     </row>
     <row r="6">
@@ -20764,7 +20764,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>30183</v>
+        <v>41175</v>
       </c>
     </row>
     <row r="7">
@@ -20799,7 +20799,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>716200</v>
+        <v>775286</v>
       </c>
     </row>
     <row r="8">
@@ -20834,7 +20834,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>320000</v>
+        <v>346400</v>
       </c>
     </row>
     <row r="9">
@@ -20869,7 +20869,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>11813</v>
+        <v>12788</v>
       </c>
     </row>
     <row r="10">
@@ -20904,7 +20904,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>12000</v>
+        <v>15588</v>
       </c>
     </row>
     <row r="11">
@@ -20939,7 +20939,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>185192</v>
+        <v>173366</v>
       </c>
     </row>
     <row r="12">
@@ -20974,7 +20974,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>20000</v>
+        <v>21650</v>
       </c>
     </row>
     <row r="13">
@@ -21009,7 +21009,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>14000</v>
+        <v>14578</v>
       </c>
     </row>
     <row r="14">
@@ -21044,7 +21044,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>140000</v>
+        <v>145782</v>
       </c>
     </row>
     <row r="15">
@@ -21079,7 +21079,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>40000</v>
+        <v>39608</v>
       </c>
     </row>
     <row r="16">
@@ -21114,7 +21114,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>200000</v>
+        <v>208260</v>
       </c>
     </row>
     <row r="17">
@@ -21149,7 +21149,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>35000</v>
+        <v>36445</v>
       </c>
     </row>
     <row r="18">
@@ -21184,7 +21184,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>11813</v>
+        <v>12301</v>
       </c>
     </row>
     <row r="19">
@@ -21219,7 +21219,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>15000</v>
+        <v>14995</v>
       </c>
     </row>
     <row r="20">
@@ -21254,7 +21254,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>3000</v>
+        <v>3124</v>
       </c>
     </row>
     <row r="21">
@@ -21289,7 +21289,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>20000</v>
+        <v>20826</v>
       </c>
     </row>
     <row r="22">
@@ -21324,7 +21324,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>14000</v>
+        <v>12844</v>
       </c>
     </row>
     <row r="23">
@@ -21359,7 +21359,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>18000</v>
+        <v>12828</v>
       </c>
     </row>
     <row r="24">
@@ -21394,7 +21394,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>40000</v>
+        <v>36294</v>
       </c>
     </row>
     <row r="25">
@@ -21429,7 +21429,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>100000</v>
+        <v>91740</v>
       </c>
     </row>
     <row r="26">
@@ -21464,7 +21464,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>120000</v>
+        <v>54429</v>
       </c>
     </row>
     <row r="27">
@@ -21499,7 +21499,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>42750</v>
+        <v>39219</v>
       </c>
     </row>
     <row r="28">
@@ -21534,7 +21534,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>40000</v>
+        <v>34895</v>
       </c>
     </row>
     <row r="29">
@@ -21569,7 +21569,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>716200</v>
+        <v>657042</v>
       </c>
     </row>
     <row r="30">
@@ -21604,7 +21604,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>320000</v>
+        <v>293568</v>
       </c>
     </row>
     <row r="31">
@@ -21639,7 +21639,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>375529</v>
+        <v>344510</v>
       </c>
     </row>
     <row r="32">
@@ -21674,7 +21674,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>200000</v>
+        <v>183480</v>
       </c>
     </row>
     <row r="33">
@@ -21709,7 +21709,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>20000</v>
+        <v>18348</v>
       </c>
     </row>
     <row r="34">
@@ -21744,7 +21744,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>11813</v>
+        <v>10837</v>
       </c>
     </row>
     <row r="35">
@@ -21779,7 +21779,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>15000</v>
+        <v>13211</v>
       </c>
     </row>
     <row r="36">
@@ -21814,7 +21814,7 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>60000</v>
+        <v>146925</v>
       </c>
     </row>
     <row r="37">
@@ -21849,7 +21849,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>14000</v>
+        <v>13422</v>
       </c>
     </row>
     <row r="38">
@@ -21884,7 +21884,7 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>100000</v>
+        <v>95870</v>
       </c>
     </row>
     <row r="39">
@@ -21919,7 +21919,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>120000</v>
+        <v>115044</v>
       </c>
     </row>
     <row r="40">
@@ -21954,7 +21954,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>42750</v>
+        <v>40984</v>
       </c>
     </row>
     <row r="41">
@@ -21989,7 +21989,7 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>40000</v>
+        <v>36466</v>
       </c>
     </row>
     <row r="42">
@@ -22024,7 +22024,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>35000</v>
+        <v>33554</v>
       </c>
     </row>
     <row r="43">
@@ -22059,7 +22059,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>11813</v>
+        <v>11325</v>
       </c>
     </row>
     <row r="44">
@@ -22094,7 +22094,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>15000</v>
+        <v>13805</v>
       </c>
     </row>
     <row r="45">
@@ -22129,7 +22129,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>3000</v>
+        <v>2876</v>
       </c>
     </row>
     <row r="46">
@@ -22164,7 +22164,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>35000</v>
+        <v>37888</v>
       </c>
     </row>
     <row r="47">
@@ -22199,7 +22199,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>35000</v>
+        <v>36445</v>
       </c>
     </row>
     <row r="48">
@@ -22234,7 +22234,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>35000</v>
+        <v>33554</v>
       </c>
     </row>
     <row r="49">
@@ -22269,7 +22269,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>35000</v>
+        <v>32109</v>
       </c>
     </row>
     <row r="50">
@@ -22339,7 +22339,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>95000</v>
+        <v>102838</v>
       </c>
     </row>
     <row r="52">
@@ -22374,7 +22374,7 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>95000</v>
+        <v>98923</v>
       </c>
     </row>
     <row r="53">
@@ -22409,7 +22409,7 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>95000</v>
+        <v>91076</v>
       </c>
     </row>
     <row r="54">
@@ -22444,7 +22444,7 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>95000</v>
+        <v>87153</v>
       </c>
     </row>
     <row r="55">
@@ -22514,7 +22514,7 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>70000</v>
+        <v>75775</v>
       </c>
     </row>
     <row r="57">
@@ -22549,7 +22549,7 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>70000</v>
+        <v>72891</v>
       </c>
     </row>
     <row r="58">
@@ -22584,7 +22584,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>70000</v>
+        <v>67109</v>
       </c>
     </row>
     <row r="59">
@@ -22619,7 +22619,7 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>70000</v>
+        <v>64218</v>
       </c>
     </row>
     <row r="60">
@@ -22689,7 +22689,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>12979</v>
+        <v>13983</v>
       </c>
     </row>
     <row r="62">
@@ -22724,7 +22724,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>12979</v>
+        <v>14561</v>
       </c>
     </row>
     <row r="63">
@@ -22759,7 +22759,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>12979</v>
+        <v>13406</v>
       </c>
     </row>
     <row r="64">
@@ -22794,7 +22794,7 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>39452</v>
+        <v>39562</v>
       </c>
     </row>
     <row r="65">
@@ -22829,7 +22829,7 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>39452</v>
+        <v>41195</v>
       </c>
     </row>
     <row r="66">
@@ -22864,7 +22864,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>39452</v>
+        <v>37928</v>
       </c>
     </row>
     <row r="67">
@@ -22899,7 +22899,7 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>44162</v>
+        <v>59330</v>
       </c>
     </row>
     <row r="68">
@@ -22934,7 +22934,7 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>44162</v>
+        <v>61780</v>
       </c>
     </row>
     <row r="69">
@@ -22969,7 +22969,7 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>44162</v>
+        <v>56879</v>
       </c>
     </row>
     <row r="70">
@@ -23039,7 +23039,7 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>42750</v>
+        <v>44516</v>
       </c>
     </row>
     <row r="72">
@@ -23074,7 +23074,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>40000</v>
+        <v>38037</v>
       </c>
     </row>
     <row r="73">
@@ -23144,7 +23144,7 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>716200</v>
+        <v>745779</v>
       </c>
     </row>
     <row r="75">
@@ -23179,7 +23179,7 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>716200</v>
+        <v>686621</v>
       </c>
     </row>
     <row r="76">
@@ -23249,7 +23249,7 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>320000</v>
+        <v>333216</v>
       </c>
     </row>
     <row r="78">
@@ -23284,7 +23284,7 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>320000</v>
+        <v>306784</v>
       </c>
     </row>
     <row r="79">
@@ -23354,7 +23354,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>15000</v>
+        <v>14400</v>
       </c>
     </row>
     <row r="81">
@@ -23389,7 +23389,7 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>185192</v>
+        <v>160154</v>
       </c>
     </row>
     <row r="82">
@@ -23424,7 +23424,7 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>185192</v>
+        <v>166768</v>
       </c>
     </row>
     <row r="83">
@@ -23459,7 +23459,7 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>185192</v>
+        <v>153539</v>
       </c>
     </row>
     <row r="84">
@@ -23529,7 +23529,7 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>20000</v>
+        <v>19174</v>
       </c>
     </row>
     <row r="86">
@@ -23564,7 +23564,7 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>20000</v>
+        <v>18348</v>
       </c>
     </row>
     <row r="87">
@@ -23634,7 +23634,7 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>14000</v>
+        <v>15155</v>
       </c>
     </row>
     <row r="89">
@@ -23704,7 +23704,7 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>140000</v>
+        <v>134218</v>
       </c>
     </row>
     <row r="91">
@@ -23739,7 +23739,7 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>140000</v>
+        <v>151550</v>
       </c>
     </row>
     <row r="92">
@@ -23774,7 +23774,7 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>140000</v>
+        <v>128436</v>
       </c>
     </row>
     <row r="93">
@@ -23844,7 +23844,7 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>200000</v>
+        <v>191740</v>
       </c>
     </row>
     <row r="95">
@@ -23879,7 +23879,7 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>200000</v>
+        <v>216500</v>
       </c>
     </row>
     <row r="96">
@@ -23949,7 +23949,7 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>35000</v>
+        <v>37888</v>
       </c>
     </row>
     <row r="98">
@@ -23984,7 +23984,7 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>35000</v>
+        <v>32109</v>
       </c>
     </row>
     <row r="99">
@@ -24054,7 +24054,7 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>3000</v>
+        <v>3248</v>
       </c>
     </row>
     <row r="101">
@@ -24089,7 +24089,7 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>3000</v>
+        <v>2752</v>
       </c>
     </row>
     <row r="102">
@@ -24159,7 +24159,7 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>100000</v>
+        <v>104130</v>
       </c>
     </row>
     <row r="104">
@@ -24194,7 +24194,7 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>100000</v>
+        <v>108250</v>
       </c>
     </row>
     <row r="105">
@@ -24264,7 +24264,7 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>375529</v>
+        <v>391038</v>
       </c>
     </row>
     <row r="107">
@@ -24299,7 +24299,7 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>375529</v>
+        <v>406510</v>
       </c>
     </row>
     <row r="108">
@@ -24334,7 +24334,7 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>375529</v>
+        <v>360020</v>
       </c>
     </row>
     <row r="109">
@@ -24404,7 +24404,7 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>20000</v>
+        <v>20826</v>
       </c>
     </row>
     <row r="111">
@@ -24439,7 +24439,7 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>20000</v>
+        <v>21650</v>
       </c>
     </row>
     <row r="112">
@@ -24474,7 +24474,7 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>20000</v>
+        <v>19174</v>
       </c>
     </row>
     <row r="113">
@@ -24544,7 +24544,7 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>120000</v>
+        <v>124956</v>
       </c>
     </row>
     <row r="115">
@@ -24579,7 +24579,7 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>120000</v>
+        <v>129900</v>
       </c>
     </row>
     <row r="116">
@@ -24614,7 +24614,7 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>120000</v>
+        <v>110088</v>
       </c>
     </row>
     <row r="117">
@@ -24649,7 +24649,7 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>5559</v>
+        <v>6018</v>
       </c>
     </row>
     <row r="118">
@@ -24684,7 +24684,7 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>5559</v>
+        <v>5789</v>
       </c>
     </row>
     <row r="119">
@@ -24719,7 +24719,7 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>5559</v>
+        <v>5329</v>
       </c>
     </row>
     <row r="120">
@@ -24754,7 +24754,7 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>5559</v>
+        <v>5100</v>
       </c>
     </row>
     <row r="121">
@@ -24824,7 +24824,7 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>3500</v>
+        <v>3789</v>
       </c>
     </row>
     <row r="123">
@@ -24859,7 +24859,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>3500</v>
+        <v>3645</v>
       </c>
     </row>
     <row r="124">
@@ -24894,7 +24894,7 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>3500</v>
+        <v>3355</v>
       </c>
     </row>
     <row r="125">
@@ -24929,7 +24929,7 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>3500</v>
+        <v>3211</v>
       </c>
     </row>
     <row r="126">
@@ -24999,7 +24999,7 @@
         </is>
       </c>
       <c r="G127" t="n">
-        <v>200000</v>
+        <v>216500</v>
       </c>
     </row>
     <row r="128">
@@ -25034,7 +25034,7 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>200000</v>
+        <v>208260</v>
       </c>
     </row>
     <row r="129">
@@ -25069,7 +25069,7 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>200000</v>
+        <v>191740</v>
       </c>
     </row>
     <row r="130">
@@ -25104,7 +25104,7 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>200000</v>
+        <v>183480</v>
       </c>
     </row>
     <row r="131">
@@ -25228,7 +25228,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>90000</v>
+        <v>93717</v>
       </c>
     </row>
     <row r="3">
@@ -25263,7 +25263,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>250000</v>
+        <v>260325</v>
       </c>
     </row>
     <row r="4">
@@ -25298,7 +25298,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>5000</v>
+        <v>5206</v>
       </c>
     </row>
     <row r="5">
@@ -25333,7 +25333,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>58450</v>
+        <v>60864</v>
       </c>
     </row>
     <row r="6">
@@ -25368,7 +25368,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>71809</v>
+        <v>74775</v>
       </c>
     </row>
     <row r="7">
@@ -25403,7 +25403,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>133427</v>
+        <v>138938</v>
       </c>
     </row>
     <row r="8">
@@ -25438,7 +25438,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>58500</v>
+        <v>60916</v>
       </c>
     </row>
     <row r="9">
@@ -25473,7 +25473,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>17880</v>
+        <v>18618</v>
       </c>
     </row>
     <row r="10">
@@ -25508,7 +25508,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>3670</v>
+        <v>3822</v>
       </c>
     </row>
     <row r="11">
@@ -25543,7 +25543,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>17880</v>
+        <v>18618</v>
       </c>
     </row>
     <row r="12">
@@ -25578,7 +25578,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>35290</v>
+        <v>36747</v>
       </c>
     </row>
     <row r="13">
@@ -25613,7 +25613,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>17000</v>
+        <v>17702</v>
       </c>
     </row>
     <row r="14">
@@ -25648,7 +25648,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>50000</v>
+        <v>52065</v>
       </c>
     </row>
     <row r="15">
@@ -25683,7 +25683,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>80000</v>
+        <v>83304</v>
       </c>
     </row>
     <row r="16">
@@ -25718,7 +25718,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>25000</v>
+        <v>26032</v>
       </c>
     </row>
     <row r="17">
@@ -25753,7 +25753,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>80000</v>
+        <v>83304</v>
       </c>
     </row>
     <row r="18">
@@ -25788,7 +25788,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>50000</v>
+        <v>52065</v>
       </c>
     </row>
     <row r="19">
@@ -25823,7 +25823,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>30000</v>
+        <v>31239</v>
       </c>
     </row>
     <row r="20">
@@ -25858,7 +25858,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>40250</v>
+        <v>41912</v>
       </c>
     </row>
     <row r="21">
@@ -25893,7 +25893,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>15000</v>
+        <v>15619</v>
       </c>
     </row>
     <row r="22">
@@ -25963,7 +25963,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>89459</v>
+        <v>93154</v>
       </c>
     </row>
     <row r="24">
@@ -25998,7 +25998,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>89459</v>
+        <v>93154</v>
       </c>
     </row>
     <row r="25">
@@ -26033,7 +26033,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>89459</v>
+        <v>93154</v>
       </c>
     </row>
     <row r="26">
@@ -26068,7 +26068,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>150000</v>
+        <v>156195</v>
       </c>
     </row>
     <row r="27">
@@ -26103,7 +26103,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>150000</v>
+        <v>156195</v>
       </c>
     </row>
     <row r="28">
@@ -26138,7 +26138,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>100000</v>
+        <v>104130</v>
       </c>
     </row>
     <row r="29">
@@ -26173,7 +26173,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>150000</v>
+        <v>156195</v>
       </c>
     </row>
     <row r="30">
@@ -26208,7 +26208,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>80000</v>
+        <v>83304</v>
       </c>
     </row>
     <row r="31">
@@ -26243,7 +26243,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>120000</v>
+        <v>124956</v>
       </c>
     </row>
     <row r="32">
@@ -26278,7 +26278,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>89459</v>
+        <v>93154</v>
       </c>
     </row>
     <row r="33">
@@ -26313,7 +26313,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>65000</v>
+        <v>67684</v>
       </c>
     </row>
     <row r="34">
@@ -26348,7 +26348,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>25000</v>
+        <v>27062</v>
       </c>
     </row>
     <row r="35">
@@ -26383,7 +26383,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>15000</v>
+        <v>16238</v>
       </c>
     </row>
     <row r="36">
@@ -26418,7 +26418,7 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>20000</v>
+        <v>21650</v>
       </c>
     </row>
     <row r="37">
@@ -26453,7 +26453,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>89459</v>
+        <v>96839</v>
       </c>
     </row>
     <row r="38">
@@ -26488,7 +26488,7 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>89459</v>
+        <v>96839</v>
       </c>
     </row>
     <row r="39">
@@ -26523,7 +26523,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>150000</v>
+        <v>162375</v>
       </c>
     </row>
     <row r="40">
@@ -26558,7 +26558,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>120000</v>
+        <v>124956</v>
       </c>
     </row>
     <row r="41">
@@ -26593,7 +26593,7 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>120000</v>
+        <v>110088</v>
       </c>
     </row>
     <row r="42">
@@ -26628,7 +26628,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>90000</v>
+        <v>82566</v>
       </c>
     </row>
     <row r="43">
@@ -26663,7 +26663,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>250000</v>
+        <v>229350</v>
       </c>
     </row>
     <row r="44">
@@ -26698,7 +26698,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>5000</v>
+        <v>4587</v>
       </c>
     </row>
     <row r="45">
@@ -26733,7 +26733,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>58450</v>
+        <v>53622</v>
       </c>
     </row>
     <row r="46">
@@ -26768,7 +26768,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>71809</v>
+        <v>65878</v>
       </c>
     </row>
     <row r="47">
@@ -26803,7 +26803,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>133427</v>
+        <v>122406</v>
       </c>
     </row>
     <row r="48">
@@ -26838,7 +26838,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>58500</v>
+        <v>53668</v>
       </c>
     </row>
     <row r="49">
@@ -26873,7 +26873,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>17880</v>
+        <v>16403</v>
       </c>
     </row>
     <row r="50">
@@ -26908,7 +26908,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>3670</v>
+        <v>3367</v>
       </c>
     </row>
     <row r="51">
@@ -26943,7 +26943,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>17880</v>
+        <v>16403</v>
       </c>
     </row>
     <row r="52">
@@ -26978,7 +26978,7 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>35290</v>
+        <v>32375</v>
       </c>
     </row>
     <row r="53">
@@ -27013,7 +27013,7 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>17000</v>
+        <v>15596</v>
       </c>
     </row>
     <row r="54">
@@ -27048,7 +27048,7 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>50000</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="55">
@@ -27083,7 +27083,7 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>80000</v>
+        <v>73392</v>
       </c>
     </row>
     <row r="56">
@@ -27118,7 +27118,7 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>25000</v>
+        <v>22935</v>
       </c>
     </row>
     <row r="57">
@@ -27153,7 +27153,7 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>80000</v>
+        <v>73392</v>
       </c>
     </row>
     <row r="58">
@@ -27188,7 +27188,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>50000</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="59">
@@ -27223,7 +27223,7 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>30000</v>
+        <v>27522</v>
       </c>
     </row>
     <row r="60">
@@ -27258,7 +27258,7 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>40250</v>
+        <v>36925</v>
       </c>
     </row>
     <row r="61">
@@ -27293,7 +27293,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>15000</v>
+        <v>13761</v>
       </c>
     </row>
     <row r="62">
@@ -27363,7 +27363,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>20000</v>
+        <v>18348</v>
       </c>
     </row>
     <row r="64">
@@ -27398,7 +27398,7 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>89459</v>
+        <v>82070</v>
       </c>
     </row>
     <row r="65">
@@ -27433,7 +27433,7 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>89459</v>
+        <v>82070</v>
       </c>
     </row>
     <row r="66">
@@ -27468,7 +27468,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>89459</v>
+        <v>82070</v>
       </c>
     </row>
     <row r="67">
@@ -27503,7 +27503,7 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>150000</v>
+        <v>137610</v>
       </c>
     </row>
     <row r="68">
@@ -27538,7 +27538,7 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>150000</v>
+        <v>137610</v>
       </c>
     </row>
     <row r="69">
@@ -27573,7 +27573,7 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>100000</v>
+        <v>91740</v>
       </c>
     </row>
     <row r="70">
@@ -27608,7 +27608,7 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>150000</v>
+        <v>137610</v>
       </c>
     </row>
     <row r="71">
@@ -27643,7 +27643,7 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>80000</v>
+        <v>73392</v>
       </c>
     </row>
     <row r="72">
@@ -27678,7 +27678,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>120000</v>
+        <v>110088</v>
       </c>
     </row>
     <row r="73">
@@ -27713,7 +27713,7 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>89459</v>
+        <v>82070</v>
       </c>
     </row>
     <row r="74">
@@ -27748,7 +27748,7 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>65000</v>
+        <v>59631</v>
       </c>
     </row>
     <row r="75">
@@ -27783,7 +27783,7 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>90000</v>
+        <v>86283</v>
       </c>
     </row>
     <row r="76">
@@ -27818,7 +27818,7 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>250000</v>
+        <v>239675</v>
       </c>
     </row>
     <row r="77">
@@ -27853,7 +27853,7 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>5000</v>
+        <v>4794</v>
       </c>
     </row>
     <row r="78">
@@ -27888,7 +27888,7 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>58450</v>
+        <v>56036</v>
       </c>
     </row>
     <row r="79">
@@ -27923,7 +27923,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>71809</v>
+        <v>68843</v>
       </c>
     </row>
     <row r="80">
@@ -27958,7 +27958,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>133427</v>
+        <v>127916</v>
       </c>
     </row>
     <row r="81">
@@ -27993,7 +27993,7 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>58500</v>
+        <v>56084</v>
       </c>
     </row>
     <row r="82">
@@ -28028,7 +28028,7 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>17880</v>
+        <v>17142</v>
       </c>
     </row>
     <row r="83">
@@ -28063,7 +28063,7 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>3670</v>
+        <v>3518</v>
       </c>
     </row>
     <row r="84">
@@ -28098,7 +28098,7 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>17880</v>
+        <v>17142</v>
       </c>
     </row>
     <row r="85">
@@ -28133,7 +28133,7 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>35290</v>
+        <v>33833</v>
       </c>
     </row>
     <row r="86">
@@ -28168,7 +28168,7 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>17000</v>
+        <v>16298</v>
       </c>
     </row>
     <row r="87">
@@ -28203,7 +28203,7 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>50000</v>
+        <v>47935</v>
       </c>
     </row>
     <row r="88">
@@ -28238,7 +28238,7 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>80000</v>
+        <v>76696</v>
       </c>
     </row>
     <row r="89">
@@ -28273,7 +28273,7 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>25000</v>
+        <v>23968</v>
       </c>
     </row>
     <row r="90">
@@ -28308,7 +28308,7 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>80000</v>
+        <v>76696</v>
       </c>
     </row>
     <row r="91">
@@ -28343,7 +28343,7 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>50000</v>
+        <v>47935</v>
       </c>
     </row>
     <row r="92">
@@ -28378,7 +28378,7 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>30000</v>
+        <v>28761</v>
       </c>
     </row>
     <row r="93">
@@ -28413,7 +28413,7 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>40250</v>
+        <v>38588</v>
       </c>
     </row>
     <row r="94">
@@ -28448,7 +28448,7 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>15000</v>
+        <v>14380</v>
       </c>
     </row>
     <row r="95">
@@ -28518,7 +28518,7 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>89459</v>
+        <v>85764</v>
       </c>
     </row>
     <row r="97">
@@ -28553,7 +28553,7 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>89459</v>
+        <v>85764</v>
       </c>
     </row>
     <row r="98">
@@ -28588,7 +28588,7 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>89459</v>
+        <v>85764</v>
       </c>
     </row>
     <row r="99">
@@ -28623,7 +28623,7 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>150000</v>
+        <v>143805</v>
       </c>
     </row>
     <row r="100">
@@ -28658,7 +28658,7 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>150000</v>
+        <v>143805</v>
       </c>
     </row>
     <row r="101">
@@ -28693,7 +28693,7 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>100000</v>
+        <v>95870</v>
       </c>
     </row>
     <row r="102">
@@ -28728,7 +28728,7 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>150000</v>
+        <v>143805</v>
       </c>
     </row>
     <row r="103">
@@ -28763,7 +28763,7 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>80000</v>
+        <v>76696</v>
       </c>
     </row>
     <row r="104">
@@ -28798,7 +28798,7 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>120000</v>
+        <v>115044</v>
       </c>
     </row>
     <row r="105">
@@ -28833,7 +28833,7 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>89459</v>
+        <v>85764</v>
       </c>
     </row>
     <row r="106">
@@ -28868,7 +28868,7 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>65000</v>
+        <v>62316</v>
       </c>
     </row>
     <row r="107">
@@ -28903,7 +28903,7 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>150000</v>
+        <v>162375</v>
       </c>
     </row>
     <row r="108">
@@ -28938,7 +28938,7 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>65000</v>
+        <v>70362</v>
       </c>
     </row>
     <row r="109">
@@ -28973,7 +28973,7 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>150000</v>
+        <v>162375</v>
       </c>
     </row>
     <row r="110">
@@ -29008,7 +29008,7 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>150000</v>
+        <v>156195</v>
       </c>
     </row>
     <row r="111">
@@ -29043,7 +29043,7 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>150000</v>
+        <v>143805</v>
       </c>
     </row>
     <row r="112">
@@ -29078,7 +29078,7 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>150000</v>
+        <v>137610</v>
       </c>
     </row>
     <row r="113">
@@ -29183,7 +29183,7 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>90000</v>
+        <v>97425</v>
       </c>
     </row>
     <row r="116">
@@ -29253,7 +29253,7 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>250000</v>
+        <v>270625</v>
       </c>
     </row>
     <row r="118">
@@ -29323,7 +29323,7 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>5000</v>
+        <v>5412</v>
       </c>
     </row>
     <row r="120">
@@ -29393,7 +29393,7 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>58450</v>
+        <v>63272</v>
       </c>
     </row>
     <row r="122">
@@ -29463,7 +29463,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>71809</v>
+        <v>77733</v>
       </c>
     </row>
     <row r="124">
@@ -29533,7 +29533,7 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>133427</v>
+        <v>144435</v>
       </c>
     </row>
     <row r="126">
@@ -29603,7 +29603,7 @@
         </is>
       </c>
       <c r="G127" t="n">
-        <v>58500</v>
+        <v>63326</v>
       </c>
     </row>
     <row r="128">
@@ -29673,7 +29673,7 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>17880</v>
+        <v>19355</v>
       </c>
     </row>
     <row r="130">
@@ -29743,7 +29743,7 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>3670</v>
+        <v>3973</v>
       </c>
     </row>
     <row r="132">
@@ -29813,7 +29813,7 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>17880</v>
+        <v>19355</v>
       </c>
     </row>
     <row r="134">
@@ -29883,7 +29883,7 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>35290</v>
+        <v>38201</v>
       </c>
     </row>
     <row r="136">
@@ -29953,7 +29953,7 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>17000</v>
+        <v>18402</v>
       </c>
     </row>
     <row r="138">
@@ -30023,7 +30023,7 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>50000</v>
+        <v>54125</v>
       </c>
     </row>
     <row r="140">
@@ -30093,7 +30093,7 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>80000</v>
+        <v>86600</v>
       </c>
     </row>
     <row r="142">
@@ -30198,7 +30198,7 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>80000</v>
+        <v>86600</v>
       </c>
     </row>
     <row r="145">
@@ -30268,7 +30268,7 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>50000</v>
+        <v>54125</v>
       </c>
     </row>
     <row r="147">
@@ -30338,7 +30338,7 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>30000</v>
+        <v>32475</v>
       </c>
     </row>
     <row r="149">
@@ -30408,7 +30408,7 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>40250</v>
+        <v>43571</v>
       </c>
     </row>
     <row r="151">
@@ -30583,7 +30583,7 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>89459</v>
+        <v>96839</v>
       </c>
     </row>
     <row r="156">
@@ -30723,7 +30723,7 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>150000</v>
+        <v>162375</v>
       </c>
     </row>
     <row r="160">
@@ -30828,7 +30828,7 @@
         </is>
       </c>
       <c r="G162" t="n">
-        <v>100000</v>
+        <v>108250</v>
       </c>
     </row>
     <row r="163">
@@ -30933,7 +30933,7 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>80000</v>
+        <v>86600</v>
       </c>
     </row>
     <row r="166">
@@ -31003,7 +31003,7 @@
         </is>
       </c>
       <c r="G167" t="n">
-        <v>120000</v>
+        <v>129900</v>
       </c>
     </row>
     <row r="168">
@@ -31073,7 +31073,7 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>89459</v>
+        <v>96839</v>
       </c>
     </row>
     <row r="170">
@@ -31178,7 +31178,7 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>20000</v>
+        <v>20826</v>
       </c>
     </row>
     <row r="173">
@@ -31213,7 +31213,7 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>20000</v>
+        <v>19174</v>
       </c>
     </row>
     <row r="174">
@@ -31283,7 +31283,7 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>120000</v>
+        <v>115044</v>
       </c>
     </row>
     <row r="176">
@@ -31318,7 +31318,7 @@
         </is>
       </c>
       <c r="G176" t="n">
-        <v>120000</v>
+        <v>129900</v>
       </c>
     </row>
   </sheetData>
@@ -31442,7 +31442,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>5280</v>
+        <v>5498</v>
       </c>
     </row>
     <row r="4">
@@ -31477,7 +31477,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3730400</v>
+        <v>3884466</v>
       </c>
     </row>
     <row r="5">
@@ -31512,7 +31512,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>219936</v>
+        <v>229019</v>
       </c>
     </row>
     <row r="6">
@@ -31547,7 +31547,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>283728</v>
+        <v>295446</v>
       </c>
     </row>
     <row r="7">
@@ -31582,7 +31582,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>70300</v>
+        <v>73203</v>
       </c>
     </row>
     <row r="8">
@@ -31617,7 +31617,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>68484</v>
+        <v>58710</v>
       </c>
     </row>
     <row r="9">
@@ -31652,7 +31652,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>289093</v>
+        <v>301033</v>
       </c>
     </row>
     <row r="10">
@@ -31687,7 +31687,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>134021</v>
+        <v>132341</v>
       </c>
     </row>
     <row r="11">
@@ -31722,7 +31722,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>33090</v>
+        <v>34457</v>
       </c>
     </row>
     <row r="12">
@@ -31757,7 +31757,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>16779</v>
+        <v>17472</v>
       </c>
     </row>
     <row r="13">
@@ -31792,7 +31792,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>67547</v>
+        <v>70337</v>
       </c>
     </row>
     <row r="14">
@@ -31827,7 +31827,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>544824</v>
+        <v>567325</v>
       </c>
     </row>
     <row r="15">
@@ -31862,7 +31862,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>457800</v>
+        <v>476707</v>
       </c>
     </row>
     <row r="16">
@@ -31897,7 +31897,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>3680000</v>
+        <v>3831984</v>
       </c>
     </row>
     <row r="17">
@@ -31932,7 +31932,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18">
@@ -31967,7 +31967,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>76275</v>
+        <v>79425</v>
       </c>
     </row>
     <row r="19">
@@ -32002,7 +32002,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>71340</v>
+        <v>74286</v>
       </c>
     </row>
     <row r="20">
@@ -32037,7 +32037,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>16990</v>
+        <v>17692</v>
       </c>
     </row>
     <row r="21">
@@ -32072,7 +32072,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>30093</v>
+        <v>31336</v>
       </c>
     </row>
     <row r="22">
@@ -32107,7 +32107,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>50688</v>
+        <v>52781</v>
       </c>
     </row>
     <row r="23">
@@ -32142,7 +32142,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>72360</v>
+        <v>75348</v>
       </c>
     </row>
     <row r="24">
@@ -32177,7 +32177,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>68000</v>
+        <v>70808</v>
       </c>
     </row>
     <row r="25">
@@ -32212,7 +32212,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>60300</v>
+        <v>62790</v>
       </c>
     </row>
     <row r="26">
@@ -32247,7 +32247,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>5400</v>
+        <v>5430</v>
       </c>
     </row>
     <row r="27">
@@ -32282,7 +32282,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>23200</v>
+        <v>24149</v>
       </c>
     </row>
     <row r="28">
@@ -32317,7 +32317,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>12400</v>
+        <v>12912</v>
       </c>
     </row>
     <row r="29">
@@ -32352,7 +32352,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>8139</v>
+        <v>8406</v>
       </c>
     </row>
     <row r="30">
@@ -32387,7 +32387,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>37699</v>
+        <v>43549</v>
       </c>
     </row>
     <row r="31">
@@ -32422,7 +32422,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>3730400</v>
+        <v>3884466</v>
       </c>
     </row>
     <row r="32">
@@ -32457,7 +32457,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>325500</v>
+        <v>338943</v>
       </c>
     </row>
     <row r="33">
@@ -32492,7 +32492,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>59935571</v>
+        <v>62410910</v>
       </c>
     </row>
     <row r="34">
@@ -32527,7 +32527,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>170892</v>
+        <v>177950</v>
       </c>
     </row>
     <row r="35">
@@ -32562,7 +32562,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>54700</v>
+        <v>56959</v>
       </c>
     </row>
     <row r="36">
@@ -32597,7 +32597,7 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>15918181</v>
+        <v>16575602</v>
       </c>
     </row>
     <row r="37">
@@ -32632,7 +32632,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>63425</v>
+        <v>66044</v>
       </c>
     </row>
     <row r="38">
@@ -32667,7 +32667,7 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>376990</v>
+        <v>392560</v>
       </c>
     </row>
     <row r="39">
@@ -32702,7 +32702,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>190955</v>
+        <v>198841</v>
       </c>
     </row>
     <row r="40">
@@ -32737,7 +32737,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>509018</v>
+        <v>530040</v>
       </c>
     </row>
     <row r="41">
@@ -32772,7 +32772,7 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>957950</v>
+        <v>997513</v>
       </c>
     </row>
     <row r="42">
@@ -32807,7 +32807,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>440494</v>
+        <v>458686</v>
       </c>
     </row>
     <row r="43">
@@ -32842,7 +32842,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>179030</v>
+        <v>186424</v>
       </c>
     </row>
     <row r="44">
@@ -32877,7 +32877,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>899300</v>
+        <v>936441</v>
       </c>
     </row>
     <row r="45">
@@ -32912,7 +32912,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>32000</v>
+        <v>33322</v>
       </c>
     </row>
     <row r="46">
@@ -32947,7 +32947,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>3962975</v>
+        <v>4126646</v>
       </c>
     </row>
     <row r="47">
@@ -32982,7 +32982,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>520000</v>
+        <v>541476</v>
       </c>
     </row>
     <row r="48">
@@ -33017,7 +33017,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>12000</v>
+        <v>12496</v>
       </c>
     </row>
     <row r="49">
@@ -33052,7 +33052,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>4024800</v>
+        <v>4191024</v>
       </c>
     </row>
     <row r="50">
@@ -33087,7 +33087,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>54652</v>
+        <v>56909</v>
       </c>
     </row>
     <row r="51">
@@ -33122,7 +33122,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>319000</v>
+        <v>332175</v>
       </c>
     </row>
     <row r="52">
@@ -33157,7 +33157,7 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>22990</v>
+        <v>23939</v>
       </c>
     </row>
     <row r="53">
@@ -33192,7 +33192,7 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>24482</v>
+        <v>24685</v>
       </c>
     </row>
     <row r="54">
@@ -33227,7 +33227,7 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>35728</v>
+        <v>44933</v>
       </c>
     </row>
     <row r="55">
@@ -33262,7 +33262,7 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>229000</v>
+        <v>238458</v>
       </c>
     </row>
     <row r="56">
@@ -33297,7 +33297,7 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>3730400</v>
+        <v>3884466</v>
       </c>
     </row>
     <row r="57">
@@ -33332,7 +33332,7 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>3730400</v>
+        <v>3884466</v>
       </c>
     </row>
     <row r="58">
@@ -33367,7 +33367,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>46750</v>
+        <v>48681</v>
       </c>
     </row>
     <row r="59">
@@ -33402,7 +33402,7 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>3650000</v>
+        <v>3800745</v>
       </c>
     </row>
     <row r="60">
@@ -33437,7 +33437,7 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>10707450</v>
+        <v>11149668</v>
       </c>
     </row>
     <row r="61">
@@ -33472,7 +33472,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>3850000</v>
+        <v>4009005</v>
       </c>
     </row>
     <row r="62">
@@ -33507,7 +33507,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>3850000</v>
+        <v>4009005</v>
       </c>
     </row>
     <row r="63">
@@ -33542,7 +33542,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>16990</v>
+        <v>17692</v>
       </c>
     </row>
     <row r="64">
@@ -33577,7 +33577,7 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>739658</v>
+        <v>770206</v>
       </c>
     </row>
     <row r="65">
@@ -33612,7 +33612,7 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>821534</v>
+        <v>855463</v>
       </c>
     </row>
     <row r="66">
@@ -33647,7 +33647,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>11098225</v>
+        <v>11556582</v>
       </c>
     </row>
     <row r="67">
@@ -33682,7 +33682,7 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>699900</v>
+        <v>728806</v>
       </c>
     </row>
     <row r="68">
@@ -33717,7 +33717,7 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>15615</v>
+        <v>16260</v>
       </c>
     </row>
     <row r="69">
@@ -33752,7 +33752,7 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>69296</v>
+        <v>72158</v>
       </c>
     </row>
     <row r="70">
@@ -33787,7 +33787,7 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>137</v>
+        <v>143</v>
       </c>
     </row>
     <row r="71">
@@ -33822,7 +33822,7 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>3690</v>
+        <v>3476</v>
       </c>
     </row>
     <row r="72">
@@ -33857,7 +33857,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>3118</v>
+        <v>3186</v>
       </c>
     </row>
     <row r="73">
@@ -33892,7 +33892,7 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>280</v>
+        <v>292</v>
       </c>
     </row>
     <row r="74">
@@ -33927,7 +33927,7 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>3990000</v>
+        <v>4154787</v>
       </c>
     </row>
     <row r="75">
@@ -33962,7 +33962,7 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>11832000</v>
+        <v>12320662</v>
       </c>
     </row>
     <row r="76">
@@ -33997,7 +33997,7 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>604500</v>
+        <v>629466</v>
       </c>
     </row>
     <row r="77">
@@ -34067,7 +34067,7 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>5280</v>
+        <v>5062</v>
       </c>
     </row>
     <row r="79">
@@ -34102,7 +34102,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>3730400</v>
+        <v>3576334</v>
       </c>
     </row>
     <row r="80">
@@ -34137,7 +34137,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>219936</v>
+        <v>210853</v>
       </c>
     </row>
     <row r="81">
@@ -34172,7 +34172,7 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>283728</v>
+        <v>272010</v>
       </c>
     </row>
     <row r="82">
@@ -34207,7 +34207,7 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>70300</v>
+        <v>67397</v>
       </c>
     </row>
     <row r="83">
@@ -34242,7 +34242,7 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>48954</v>
+        <v>54053</v>
       </c>
     </row>
     <row r="84">
@@ -34277,7 +34277,7 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>289093</v>
+        <v>277153</v>
       </c>
     </row>
     <row r="85">
@@ -34312,7 +34312,7 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>99377</v>
+        <v>121843</v>
       </c>
     </row>
     <row r="86">
@@ -34347,7 +34347,7 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>33090</v>
+        <v>31723</v>
       </c>
     </row>
     <row r="87">
@@ -34382,7 +34382,7 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>16779</v>
+        <v>16086</v>
       </c>
     </row>
     <row r="88">
@@ -34417,7 +34417,7 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>67547</v>
+        <v>64757</v>
       </c>
     </row>
     <row r="89">
@@ -34452,7 +34452,7 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>544824</v>
+        <v>522323</v>
       </c>
     </row>
     <row r="90">
@@ -34487,7 +34487,7 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>457800</v>
+        <v>438893</v>
       </c>
     </row>
     <row r="91">
@@ -34522,7 +34522,7 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>3680000</v>
+        <v>3528016</v>
       </c>
     </row>
     <row r="92">
@@ -34557,7 +34557,7 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="93">
@@ -34592,7 +34592,7 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>76275</v>
+        <v>73125</v>
       </c>
     </row>
     <row r="94">
@@ -34627,7 +34627,7 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>71340</v>
+        <v>68394</v>
       </c>
     </row>
     <row r="95">
@@ -34662,7 +34662,7 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>16990</v>
+        <v>16288</v>
       </c>
     </row>
     <row r="96">
@@ -34697,7 +34697,7 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>30093</v>
+        <v>28850</v>
       </c>
     </row>
     <row r="97">
@@ -34732,7 +34732,7 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>50688</v>
+        <v>48595</v>
       </c>
     </row>
     <row r="98">
@@ -34767,7 +34767,7 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>72360</v>
+        <v>69372</v>
       </c>
     </row>
     <row r="99">
@@ -34802,7 +34802,7 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>68000</v>
+        <v>65192</v>
       </c>
     </row>
     <row r="100">
@@ -34837,7 +34837,7 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>60300</v>
+        <v>57810</v>
       </c>
     </row>
     <row r="101">
@@ -34872,7 +34872,7 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>4465</v>
+        <v>4999</v>
       </c>
     </row>
     <row r="102">
@@ -34907,7 +34907,7 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>23189</v>
+        <v>22233</v>
       </c>
     </row>
     <row r="103">
@@ -34942,7 +34942,7 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>12400</v>
+        <v>11888</v>
       </c>
     </row>
     <row r="104">
@@ -34977,7 +34977,7 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>8139</v>
+        <v>7739</v>
       </c>
     </row>
     <row r="105">
@@ -35012,7 +35012,7 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>40071</v>
+        <v>40095</v>
       </c>
     </row>
     <row r="106">
@@ -35047,7 +35047,7 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>3730400</v>
+        <v>3576334</v>
       </c>
     </row>
     <row r="107">
@@ -35082,7 +35082,7 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>325500</v>
+        <v>312057</v>
       </c>
     </row>
     <row r="108">
@@ -35117,7 +35117,7 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>59935571</v>
+        <v>57460232</v>
       </c>
     </row>
     <row r="109">
@@ -35152,7 +35152,7 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>170892</v>
+        <v>163834</v>
       </c>
     </row>
     <row r="110">
@@ -35187,7 +35187,7 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>54700</v>
+        <v>52441</v>
       </c>
     </row>
     <row r="111">
@@ -35222,7 +35222,7 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>15918181</v>
+        <v>15260760</v>
       </c>
     </row>
     <row r="112">
@@ -35257,7 +35257,7 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>63425</v>
+        <v>60806</v>
       </c>
     </row>
     <row r="113">
@@ -35292,7 +35292,7 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>376990</v>
+        <v>361420</v>
       </c>
     </row>
     <row r="114">
@@ -35327,7 +35327,7 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>190955</v>
+        <v>183069</v>
       </c>
     </row>
     <row r="115">
@@ -35362,7 +35362,7 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>509018</v>
+        <v>487996</v>
       </c>
     </row>
     <row r="116">
@@ -35397,7 +35397,7 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>957950</v>
+        <v>918387</v>
       </c>
     </row>
     <row r="117">
@@ -35432,7 +35432,7 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>440494</v>
+        <v>422302</v>
       </c>
     </row>
     <row r="118">
@@ -35467,7 +35467,7 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>179030</v>
+        <v>171636</v>
       </c>
     </row>
     <row r="119">
@@ -35502,7 +35502,7 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>899300</v>
+        <v>862159</v>
       </c>
     </row>
     <row r="120">
@@ -35537,7 +35537,7 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>32000</v>
+        <v>30678</v>
       </c>
     </row>
     <row r="121">
@@ -35572,7 +35572,7 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>3962975</v>
+        <v>3799304</v>
       </c>
     </row>
     <row r="122">
@@ -35607,7 +35607,7 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>520000</v>
+        <v>498524</v>
       </c>
     </row>
     <row r="123">
@@ -35642,7 +35642,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>12000</v>
+        <v>11504</v>
       </c>
     </row>
     <row r="124">
@@ -35677,7 +35677,7 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>4024800</v>
+        <v>3858576</v>
       </c>
     </row>
     <row r="125">
@@ -35712,7 +35712,7 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>54652</v>
+        <v>52395</v>
       </c>
     </row>
     <row r="126">
@@ -35747,7 +35747,7 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>319000</v>
+        <v>305825</v>
       </c>
     </row>
     <row r="127">
@@ -35782,7 +35782,7 @@
         </is>
       </c>
       <c r="G127" t="n">
-        <v>22990</v>
+        <v>22041</v>
       </c>
     </row>
     <row r="128">
@@ -35817,7 +35817,7 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>22992</v>
+        <v>22727</v>
       </c>
     </row>
     <row r="129">
@@ -35852,7 +35852,7 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>45007</v>
+        <v>41369</v>
       </c>
     </row>
     <row r="130">
@@ -35887,7 +35887,7 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>229000</v>
+        <v>219542</v>
       </c>
     </row>
     <row r="131">
@@ -35922,7 +35922,7 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>3730400</v>
+        <v>3576334</v>
       </c>
     </row>
     <row r="132">
@@ -35957,7 +35957,7 @@
         </is>
       </c>
       <c r="G132" t="n">
-        <v>3730400</v>
+        <v>3576334</v>
       </c>
     </row>
     <row r="133">
@@ -35992,7 +35992,7 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>46750</v>
+        <v>44819</v>
       </c>
     </row>
     <row r="134">
@@ -36027,7 +36027,7 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>3650000</v>
+        <v>3499255</v>
       </c>
     </row>
     <row r="135">
@@ -36062,7 +36062,7 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>10707450</v>
+        <v>10265232</v>
       </c>
     </row>
     <row r="136">
@@ -36097,7 +36097,7 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>3850000</v>
+        <v>3690995</v>
       </c>
     </row>
     <row r="137">
@@ -36132,7 +36132,7 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>3850000</v>
+        <v>3690995</v>
       </c>
     </row>
     <row r="138">
@@ -36167,7 +36167,7 @@
         </is>
       </c>
       <c r="G138" t="n">
-        <v>16990</v>
+        <v>16288</v>
       </c>
     </row>
     <row r="139">
@@ -36202,7 +36202,7 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>739658</v>
+        <v>709110</v>
       </c>
     </row>
     <row r="140">
@@ -36237,7 +36237,7 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>821534</v>
+        <v>787605</v>
       </c>
     </row>
     <row r="141">
@@ -36272,7 +36272,7 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>11098225</v>
+        <v>10639868</v>
       </c>
     </row>
     <row r="142">
@@ -36307,7 +36307,7 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>699900</v>
+        <v>670994</v>
       </c>
     </row>
     <row r="143">
@@ -36342,7 +36342,7 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>15615</v>
+        <v>14970</v>
       </c>
     </row>
     <row r="144">
@@ -36377,7 +36377,7 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>69296</v>
+        <v>66434</v>
       </c>
     </row>
     <row r="145">
@@ -36412,7 +36412,7 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="146">
@@ -36447,7 +36447,7 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>3250</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="147">
@@ -36482,7 +36482,7 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>2822</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="148">
@@ -36517,7 +36517,7 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>280</v>
+        <v>268</v>
       </c>
     </row>
     <row r="149">
@@ -36552,7 +36552,7 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>3990000</v>
+        <v>3825213</v>
       </c>
     </row>
     <row r="150">
@@ -36587,7 +36587,7 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>11832000</v>
+        <v>11343338</v>
       </c>
     </row>
     <row r="151">
@@ -36622,7 +36622,7 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>604500</v>
+        <v>579534</v>
       </c>
     </row>
     <row r="152">
@@ -36692,7 +36692,7 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>5280</v>
+        <v>4844</v>
       </c>
     </row>
     <row r="154">
@@ -36727,7 +36727,7 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>3730400</v>
+        <v>3422269</v>
       </c>
     </row>
     <row r="155">
@@ -36762,7 +36762,7 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>219936</v>
+        <v>201769</v>
       </c>
     </row>
     <row r="156">
@@ -36797,7 +36797,7 @@
         </is>
       </c>
       <c r="G156" t="n">
-        <v>283728</v>
+        <v>260292</v>
       </c>
     </row>
     <row r="157">
@@ -36832,7 +36832,7 @@
         </is>
       </c>
       <c r="G157" t="n">
-        <v>70300</v>
+        <v>64493</v>
       </c>
     </row>
     <row r="158">
@@ -36867,7 +36867,7 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>54823</v>
+        <v>51724</v>
       </c>
     </row>
     <row r="159">
@@ -36902,7 +36902,7 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>289093</v>
+        <v>265214</v>
       </c>
     </row>
     <row r="160">
@@ -36937,7 +36937,7 @@
         </is>
       </c>
       <c r="G160" t="n">
-        <v>134021</v>
+        <v>116594</v>
       </c>
     </row>
     <row r="161">
@@ -36972,7 +36972,7 @@
         </is>
       </c>
       <c r="G161" t="n">
-        <v>33090</v>
+        <v>30357</v>
       </c>
     </row>
     <row r="162">
@@ -37007,7 +37007,7 @@
         </is>
       </c>
       <c r="G162" t="n">
-        <v>16779</v>
+        <v>15393</v>
       </c>
     </row>
     <row r="163">
@@ -37042,7 +37042,7 @@
         </is>
       </c>
       <c r="G163" t="n">
-        <v>67547</v>
+        <v>61968</v>
       </c>
     </row>
     <row r="164">
@@ -37077,7 +37077,7 @@
         </is>
       </c>
       <c r="G164" t="n">
-        <v>544824</v>
+        <v>499822</v>
       </c>
     </row>
     <row r="165">
@@ -37112,7 +37112,7 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>457800</v>
+        <v>419986</v>
       </c>
     </row>
     <row r="166">
@@ -37147,7 +37147,7 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>3680000</v>
+        <v>3376032</v>
       </c>
     </row>
     <row r="167">
@@ -37182,7 +37182,7 @@
         </is>
       </c>
       <c r="G167" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="168">
@@ -37217,7 +37217,7 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>76275</v>
+        <v>69975</v>
       </c>
     </row>
     <row r="169">
@@ -37252,7 +37252,7 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>71340</v>
+        <v>65447</v>
       </c>
     </row>
     <row r="170">
@@ -37287,7 +37287,7 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>16990</v>
+        <v>15587</v>
       </c>
     </row>
     <row r="171">
@@ -37322,7 +37322,7 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>30093</v>
+        <v>27607</v>
       </c>
     </row>
     <row r="172">
@@ -37357,7 +37357,7 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>50688</v>
+        <v>46501</v>
       </c>
     </row>
     <row r="173">
@@ -37392,7 +37392,7 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>72360</v>
+        <v>66383</v>
       </c>
     </row>
     <row r="174">
@@ -37427,7 +37427,7 @@
         </is>
       </c>
       <c r="G174" t="n">
-        <v>68000</v>
+        <v>62383</v>
       </c>
     </row>
     <row r="175">
@@ -37462,7 +37462,7 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>60300</v>
+        <v>55319</v>
       </c>
     </row>
     <row r="176">
@@ -37497,7 +37497,7 @@
         </is>
       </c>
       <c r="G176" t="n">
-        <v>5402</v>
+        <v>4784</v>
       </c>
     </row>
     <row r="177">
@@ -37532,7 +37532,7 @@
         </is>
       </c>
       <c r="G177" t="n">
-        <v>23189</v>
+        <v>21276</v>
       </c>
     </row>
     <row r="178">
@@ -37567,7 +37567,7 @@
         </is>
       </c>
       <c r="G178" t="n">
-        <v>12400</v>
+        <v>11376</v>
       </c>
     </row>
     <row r="179">
@@ -37602,7 +37602,7 @@
         </is>
       </c>
       <c r="G179" t="n">
-        <v>8028</v>
+        <v>7406</v>
       </c>
     </row>
     <row r="180">
@@ -37637,7 +37637,7 @@
         </is>
       </c>
       <c r="G180" t="n">
-        <v>43780</v>
+        <v>38368</v>
       </c>
     </row>
     <row r="181">
@@ -37672,7 +37672,7 @@
         </is>
       </c>
       <c r="G181" t="n">
-        <v>3730400</v>
+        <v>3422269</v>
       </c>
     </row>
     <row r="182">
@@ -37707,7 +37707,7 @@
         </is>
       </c>
       <c r="G182" t="n">
-        <v>325500</v>
+        <v>298614</v>
       </c>
     </row>
     <row r="183">
@@ -37742,7 +37742,7 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>59935571</v>
+        <v>54984893</v>
       </c>
     </row>
     <row r="184">
@@ -37777,7 +37777,7 @@
         </is>
       </c>
       <c r="G184" t="n">
-        <v>170892</v>
+        <v>156776</v>
       </c>
     </row>
     <row r="185">
@@ -37812,7 +37812,7 @@
         </is>
       </c>
       <c r="G185" t="n">
-        <v>54700</v>
+        <v>50182</v>
       </c>
     </row>
     <row r="186">
@@ -37847,7 +37847,7 @@
         </is>
       </c>
       <c r="G186" t="n">
-        <v>15918181</v>
+        <v>14603339</v>
       </c>
     </row>
     <row r="187">
@@ -37882,7 +37882,7 @@
         </is>
       </c>
       <c r="G187" t="n">
-        <v>63425</v>
+        <v>58186</v>
       </c>
     </row>
     <row r="188">
@@ -37917,7 +37917,7 @@
         </is>
       </c>
       <c r="G188" t="n">
-        <v>376990</v>
+        <v>345851</v>
       </c>
     </row>
     <row r="189">
@@ -37952,7 +37952,7 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>190955</v>
+        <v>175182</v>
       </c>
     </row>
     <row r="190">
@@ -37987,7 +37987,7 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>509018</v>
+        <v>466973</v>
       </c>
     </row>
     <row r="191">
@@ -38022,7 +38022,7 @@
         </is>
       </c>
       <c r="G191" t="n">
-        <v>957950</v>
+        <v>878823</v>
       </c>
     </row>
     <row r="192">
@@ -38057,7 +38057,7 @@
         </is>
       </c>
       <c r="G192" t="n">
-        <v>440494</v>
+        <v>404109</v>
       </c>
     </row>
     <row r="193">
@@ -38092,7 +38092,7 @@
         </is>
       </c>
       <c r="G193" t="n">
-        <v>179030</v>
+        <v>164242</v>
       </c>
     </row>
     <row r="194">
@@ -38127,7 +38127,7 @@
         </is>
       </c>
       <c r="G194" t="n">
-        <v>899300</v>
+        <v>825018</v>
       </c>
     </row>
     <row r="195">
@@ -38162,7 +38162,7 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>32000</v>
+        <v>29357</v>
       </c>
     </row>
     <row r="196">
@@ -38197,7 +38197,7 @@
         </is>
       </c>
       <c r="G196" t="n">
-        <v>3962975</v>
+        <v>3635633</v>
       </c>
     </row>
     <row r="197">
@@ -38232,7 +38232,7 @@
         </is>
       </c>
       <c r="G197" t="n">
-        <v>520000</v>
+        <v>477048</v>
       </c>
     </row>
     <row r="198">
@@ -38267,7 +38267,7 @@
         </is>
       </c>
       <c r="G198" t="n">
-        <v>12000</v>
+        <v>11009</v>
       </c>
     </row>
     <row r="199">
@@ -38302,7 +38302,7 @@
         </is>
       </c>
       <c r="G199" t="n">
-        <v>4024800</v>
+        <v>3692352</v>
       </c>
     </row>
     <row r="200">
@@ -38337,7 +38337,7 @@
         </is>
       </c>
       <c r="G200" t="n">
-        <v>54652</v>
+        <v>50138</v>
       </c>
     </row>
     <row r="201">
@@ -38372,7 +38372,7 @@
         </is>
       </c>
       <c r="G201" t="n">
-        <v>319000</v>
+        <v>292651</v>
       </c>
     </row>
     <row r="202">
@@ -38407,7 +38407,7 @@
         </is>
       </c>
       <c r="G202" t="n">
-        <v>22990</v>
+        <v>21091</v>
       </c>
     </row>
     <row r="203">
@@ -38442,7 +38442,7 @@
         </is>
       </c>
       <c r="G203" t="n">
-        <v>23686</v>
+        <v>21748</v>
       </c>
     </row>
     <row r="204">
@@ -38477,7 +38477,7 @@
         </is>
       </c>
       <c r="G204" t="n">
-        <v>45007</v>
+        <v>39587</v>
       </c>
     </row>
     <row r="205">
@@ -38512,7 +38512,7 @@
         </is>
       </c>
       <c r="G205" t="n">
-        <v>229000</v>
+        <v>210085</v>
       </c>
     </row>
     <row r="206">
@@ -38547,7 +38547,7 @@
         </is>
       </c>
       <c r="G206" t="n">
-        <v>3730400</v>
+        <v>3422269</v>
       </c>
     </row>
     <row r="207">
@@ -38582,7 +38582,7 @@
         </is>
       </c>
       <c r="G207" t="n">
-        <v>3730400</v>
+        <v>3422269</v>
       </c>
     </row>
     <row r="208">
@@ -38617,7 +38617,7 @@
         </is>
       </c>
       <c r="G208" t="n">
-        <v>46750</v>
+        <v>42888</v>
       </c>
     </row>
     <row r="209">
@@ -38652,7 +38652,7 @@
         </is>
       </c>
       <c r="G209" t="n">
-        <v>3650000</v>
+        <v>3348510</v>
       </c>
     </row>
     <row r="210">
@@ -38687,7 +38687,7 @@
         </is>
       </c>
       <c r="G210" t="n">
-        <v>10707450</v>
+        <v>9823015</v>
       </c>
     </row>
     <row r="211">
@@ -38722,7 +38722,7 @@
         </is>
       </c>
       <c r="G211" t="n">
-        <v>3850000</v>
+        <v>3531990</v>
       </c>
     </row>
     <row r="212">
@@ -38757,7 +38757,7 @@
         </is>
       </c>
       <c r="G212" t="n">
-        <v>3850000</v>
+        <v>3531990</v>
       </c>
     </row>
     <row r="213">
@@ -38792,7 +38792,7 @@
         </is>
       </c>
       <c r="G213" t="n">
-        <v>16990</v>
+        <v>15587</v>
       </c>
     </row>
     <row r="214">
@@ -38827,7 +38827,7 @@
         </is>
       </c>
       <c r="G214" t="n">
-        <v>739658</v>
+        <v>678562</v>
       </c>
     </row>
     <row r="215">
@@ -38862,7 +38862,7 @@
         </is>
       </c>
       <c r="G215" t="n">
-        <v>821534</v>
+        <v>753675</v>
       </c>
     </row>
     <row r="216">
@@ -38897,7 +38897,7 @@
         </is>
       </c>
       <c r="G216" t="n">
-        <v>11098225</v>
+        <v>10181512</v>
       </c>
     </row>
     <row r="217">
@@ -38932,7 +38932,7 @@
         </is>
       </c>
       <c r="G217" t="n">
-        <v>699900</v>
+        <v>642088</v>
       </c>
     </row>
     <row r="218">
@@ -38967,7 +38967,7 @@
         </is>
       </c>
       <c r="G218" t="n">
-        <v>15615</v>
+        <v>14325</v>
       </c>
     </row>
     <row r="219">
@@ -39002,7 +39002,7 @@
         </is>
       </c>
       <c r="G219" t="n">
-        <v>69296</v>
+        <v>63572</v>
       </c>
     </row>
     <row r="220">
@@ -39037,7 +39037,7 @@
         </is>
       </c>
       <c r="G220" t="n">
-        <v>137</v>
+        <v>126</v>
       </c>
     </row>
     <row r="221">
@@ -39072,7 +39072,7 @@
         </is>
       </c>
       <c r="G221" t="n">
-        <v>3250</v>
+        <v>3062</v>
       </c>
     </row>
     <row r="222">
@@ -39107,7 +39107,7 @@
         </is>
       </c>
       <c r="G222" t="n">
-        <v>3120</v>
+        <v>2807</v>
       </c>
     </row>
     <row r="223">
@@ -39142,7 +39142,7 @@
         </is>
       </c>
       <c r="G223" t="n">
-        <v>280</v>
+        <v>257</v>
       </c>
     </row>
     <row r="224">
@@ -39177,7 +39177,7 @@
         </is>
       </c>
       <c r="G224" t="n">
-        <v>3990000</v>
+        <v>3660426</v>
       </c>
     </row>
     <row r="225">
@@ -39212,7 +39212,7 @@
         </is>
       </c>
       <c r="G225" t="n">
-        <v>11832000</v>
+        <v>10854677</v>
       </c>
     </row>
     <row r="226">
@@ -39247,7 +39247,7 @@
         </is>
       </c>
       <c r="G226" t="n">
-        <v>604500</v>
+        <v>554568</v>
       </c>
     </row>
     <row r="227">
@@ -39492,7 +39492,7 @@
         </is>
       </c>
       <c r="G233" t="n">
-        <v>54823</v>
+        <v>56381</v>
       </c>
     </row>
     <row r="234">
@@ -39562,7 +39562,7 @@
         </is>
       </c>
       <c r="G235" t="n">
-        <v>134021</v>
+        <v>127092</v>
       </c>
     </row>
     <row r="236">
@@ -40122,7 +40122,7 @@
         </is>
       </c>
       <c r="G251" t="n">
-        <v>5402</v>
+        <v>5214</v>
       </c>
     </row>
     <row r="252">
@@ -40157,7 +40157,7 @@
         </is>
       </c>
       <c r="G252" t="n">
-        <v>23189</v>
+        <v>23191</v>
       </c>
     </row>
     <row r="253">
@@ -40227,7 +40227,7 @@
         </is>
       </c>
       <c r="G254" t="n">
-        <v>8028</v>
+        <v>8072</v>
       </c>
     </row>
     <row r="255">
@@ -40262,7 +40262,7 @@
         </is>
       </c>
       <c r="G255" t="n">
-        <v>43780</v>
+        <v>41822</v>
       </c>
     </row>
     <row r="256">
@@ -41067,7 +41067,7 @@
         </is>
       </c>
       <c r="G278" t="n">
-        <v>23686</v>
+        <v>23706</v>
       </c>
     </row>
     <row r="279">
@@ -41102,7 +41102,7 @@
         </is>
       </c>
       <c r="G279" t="n">
-        <v>45007</v>
+        <v>43151</v>
       </c>
     </row>
     <row r="280">
@@ -41697,7 +41697,7 @@
         </is>
       </c>
       <c r="G296" t="n">
-        <v>3250</v>
+        <v>3338</v>
       </c>
     </row>
     <row r="297">
@@ -41732,7 +41732,7 @@
         </is>
       </c>
       <c r="G297" t="n">
-        <v>3120</v>
+        <v>3060</v>
       </c>
     </row>
     <row r="298">
@@ -41942,7 +41942,7 @@
         </is>
       </c>
       <c r="G303" t="n">
-        <v>5280</v>
+        <v>5716</v>
       </c>
     </row>
     <row r="304">
@@ -41977,7 +41977,7 @@
         </is>
       </c>
       <c r="G304" t="n">
-        <v>3730400</v>
+        <v>4038158</v>
       </c>
     </row>
     <row r="305">
@@ -42012,7 +42012,7 @@
         </is>
       </c>
       <c r="G305" t="n">
-        <v>219936</v>
+        <v>238081</v>
       </c>
     </row>
     <row r="306">
@@ -42047,7 +42047,7 @@
         </is>
       </c>
       <c r="G306" t="n">
-        <v>283728</v>
+        <v>307136</v>
       </c>
     </row>
     <row r="307">
@@ -42082,7 +42082,7 @@
         </is>
       </c>
       <c r="G307" t="n">
-        <v>70300</v>
+        <v>76100</v>
       </c>
     </row>
     <row r="308">
@@ -42117,7 +42117,7 @@
         </is>
       </c>
       <c r="G308" t="n">
-        <v>54823</v>
+        <v>61033</v>
       </c>
     </row>
     <row r="309">
@@ -42152,7 +42152,7 @@
         </is>
       </c>
       <c r="G309" t="n">
-        <v>289093</v>
+        <v>312943</v>
       </c>
     </row>
     <row r="310">
@@ -42187,7 +42187,7 @@
         </is>
       </c>
       <c r="G310" t="n">
-        <v>134021</v>
+        <v>137577</v>
       </c>
     </row>
     <row r="311">
@@ -42222,7 +42222,7 @@
         </is>
       </c>
       <c r="G311" t="n">
-        <v>33090</v>
+        <v>35820</v>
       </c>
     </row>
     <row r="312">
@@ -42257,7 +42257,7 @@
         </is>
       </c>
       <c r="G312" t="n">
-        <v>16779</v>
+        <v>18163</v>
       </c>
     </row>
     <row r="313">
@@ -42292,7 +42292,7 @@
         </is>
       </c>
       <c r="G313" t="n">
-        <v>67547</v>
+        <v>73120</v>
       </c>
     </row>
     <row r="314">
@@ -42327,7 +42327,7 @@
         </is>
       </c>
       <c r="G314" t="n">
-        <v>544824</v>
+        <v>589772</v>
       </c>
     </row>
     <row r="315">
@@ -42362,7 +42362,7 @@
         </is>
       </c>
       <c r="G315" t="n">
-        <v>457800</v>
+        <v>495568</v>
       </c>
     </row>
     <row r="316">
@@ -42397,7 +42397,7 @@
         </is>
       </c>
       <c r="G316" t="n">
-        <v>3680000</v>
+        <v>3983600</v>
       </c>
     </row>
     <row r="317">
@@ -42432,7 +42432,7 @@
         </is>
       </c>
       <c r="G317" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="318">
@@ -42467,7 +42467,7 @@
         </is>
       </c>
       <c r="G318" t="n">
-        <v>76275</v>
+        <v>82568</v>
       </c>
     </row>
     <row r="319">
@@ -42502,7 +42502,7 @@
         </is>
       </c>
       <c r="G319" t="n">
-        <v>71340</v>
+        <v>77226</v>
       </c>
     </row>
     <row r="320">
@@ -42537,7 +42537,7 @@
         </is>
       </c>
       <c r="G320" t="n">
-        <v>16990</v>
+        <v>18392</v>
       </c>
     </row>
     <row r="321">
@@ -42572,7 +42572,7 @@
         </is>
       </c>
       <c r="G321" t="n">
-        <v>30093</v>
+        <v>32576</v>
       </c>
     </row>
     <row r="322">
@@ -42607,7 +42607,7 @@
         </is>
       </c>
       <c r="G322" t="n">
-        <v>50688</v>
+        <v>54870</v>
       </c>
     </row>
     <row r="323">
@@ -42642,7 +42642,7 @@
         </is>
       </c>
       <c r="G323" t="n">
-        <v>72360</v>
+        <v>78330</v>
       </c>
     </row>
     <row r="324">
@@ -42677,7 +42677,7 @@
         </is>
       </c>
       <c r="G324" t="n">
-        <v>68000</v>
+        <v>73610</v>
       </c>
     </row>
     <row r="325">
@@ -42712,7 +42712,7 @@
         </is>
       </c>
       <c r="G325" t="n">
-        <v>60300</v>
+        <v>65275</v>
       </c>
     </row>
     <row r="326">
@@ -42747,7 +42747,7 @@
         </is>
       </c>
       <c r="G326" t="n">
-        <v>5402</v>
+        <v>5644</v>
       </c>
     </row>
     <row r="327">
@@ -42782,7 +42782,7 @@
         </is>
       </c>
       <c r="G327" t="n">
-        <v>23189</v>
+        <v>25104</v>
       </c>
     </row>
     <row r="328">
@@ -42817,7 +42817,7 @@
         </is>
       </c>
       <c r="G328" t="n">
-        <v>12400</v>
+        <v>13423</v>
       </c>
     </row>
     <row r="329">
@@ -42852,7 +42852,7 @@
         </is>
       </c>
       <c r="G329" t="n">
-        <v>8028</v>
+        <v>8738</v>
       </c>
     </row>
     <row r="330">
@@ -42887,7 +42887,7 @@
         </is>
       </c>
       <c r="G330" t="n">
-        <v>43780</v>
+        <v>45272</v>
       </c>
     </row>
     <row r="331">
@@ -42922,7 +42922,7 @@
         </is>
       </c>
       <c r="G331" t="n">
-        <v>3730400</v>
+        <v>4038158</v>
       </c>
     </row>
     <row r="332">
@@ -42957,7 +42957,7 @@
         </is>
       </c>
       <c r="G332" t="n">
-        <v>325500</v>
+        <v>352354</v>
       </c>
     </row>
     <row r="333">
@@ -42992,7 +42992,7 @@
         </is>
       </c>
       <c r="G333" t="n">
-        <v>59935571</v>
+        <v>64880256</v>
       </c>
     </row>
     <row r="334">
@@ -43027,7 +43027,7 @@
         </is>
       </c>
       <c r="G334" t="n">
-        <v>170892</v>
+        <v>184991</v>
       </c>
     </row>
     <row r="335">
@@ -43062,7 +43062,7 @@
         </is>
       </c>
       <c r="G335" t="n">
-        <v>54700</v>
+        <v>59213</v>
       </c>
     </row>
     <row r="336">
@@ -43097,7 +43097,7 @@
         </is>
       </c>
       <c r="G336" t="n">
-        <v>15918181</v>
+        <v>17231431</v>
       </c>
     </row>
     <row r="337">
@@ -43132,7 +43132,7 @@
         </is>
       </c>
       <c r="G337" t="n">
-        <v>63425</v>
+        <v>68658</v>
       </c>
     </row>
     <row r="338">
@@ -43167,7 +43167,7 @@
         </is>
       </c>
       <c r="G338" t="n">
-        <v>376990</v>
+        <v>408092</v>
       </c>
     </row>
     <row r="339">
@@ -43202,7 +43202,7 @@
         </is>
       </c>
       <c r="G339" t="n">
-        <v>190955</v>
+        <v>206709</v>
       </c>
     </row>
     <row r="340">
@@ -43237,7 +43237,7 @@
         </is>
       </c>
       <c r="G340" t="n">
-        <v>509018</v>
+        <v>551012</v>
       </c>
     </row>
     <row r="341">
@@ -43272,7 +43272,7 @@
         </is>
       </c>
       <c r="G341" t="n">
-        <v>957950</v>
+        <v>1036981</v>
       </c>
     </row>
     <row r="342">
@@ -43307,7 +43307,7 @@
         </is>
       </c>
       <c r="G342" t="n">
-        <v>440494</v>
+        <v>476835</v>
       </c>
     </row>
     <row r="343">
@@ -43342,7 +43342,7 @@
         </is>
       </c>
       <c r="G343" t="n">
-        <v>179030</v>
+        <v>193800</v>
       </c>
     </row>
     <row r="344">
@@ -43377,7 +43377,7 @@
         </is>
       </c>
       <c r="G344" t="n">
-        <v>899300</v>
+        <v>973492</v>
       </c>
     </row>
     <row r="345">
@@ -43412,7 +43412,7 @@
         </is>
       </c>
       <c r="G345" t="n">
-        <v>32000</v>
+        <v>34640</v>
       </c>
     </row>
     <row r="346">
@@ -43447,7 +43447,7 @@
         </is>
       </c>
       <c r="G346" t="n">
-        <v>3962975</v>
+        <v>4289920</v>
       </c>
     </row>
     <row r="347">
@@ -43482,7 +43482,7 @@
         </is>
       </c>
       <c r="G347" t="n">
-        <v>520000</v>
+        <v>562900</v>
       </c>
     </row>
     <row r="348">
@@ -43517,7 +43517,7 @@
         </is>
       </c>
       <c r="G348" t="n">
-        <v>12000</v>
+        <v>12990</v>
       </c>
     </row>
     <row r="349">
@@ -43552,7 +43552,7 @@
         </is>
       </c>
       <c r="G349" t="n">
-        <v>4024800</v>
+        <v>4356846</v>
       </c>
     </row>
     <row r="350">
@@ -43587,7 +43587,7 @@
         </is>
       </c>
       <c r="G350" t="n">
-        <v>54652</v>
+        <v>59161</v>
       </c>
     </row>
     <row r="351">
@@ -43622,7 +43622,7 @@
         </is>
       </c>
       <c r="G351" t="n">
-        <v>319000</v>
+        <v>345318</v>
       </c>
     </row>
     <row r="352">
@@ -43657,7 +43657,7 @@
         </is>
       </c>
       <c r="G352" t="n">
-        <v>22990</v>
+        <v>24887</v>
       </c>
     </row>
     <row r="353">
@@ -43692,7 +43692,7 @@
         </is>
       </c>
       <c r="G353" t="n">
-        <v>23686</v>
+        <v>25662</v>
       </c>
     </row>
     <row r="354">
@@ -43727,7 +43727,7 @@
         </is>
       </c>
       <c r="G354" t="n">
-        <v>45007</v>
+        <v>46711</v>
       </c>
     </row>
     <row r="355">
@@ -43762,7 +43762,7 @@
         </is>
       </c>
       <c r="G355" t="n">
-        <v>229000</v>
+        <v>247892</v>
       </c>
     </row>
     <row r="356">
@@ -43797,7 +43797,7 @@
         </is>
       </c>
       <c r="G356" t="n">
-        <v>3730400</v>
+        <v>4038158</v>
       </c>
     </row>
     <row r="357">
@@ -43832,7 +43832,7 @@
         </is>
       </c>
       <c r="G357" t="n">
-        <v>3730400</v>
+        <v>4038158</v>
       </c>
     </row>
     <row r="358">
@@ -43867,7 +43867,7 @@
         </is>
       </c>
       <c r="G358" t="n">
-        <v>46750</v>
+        <v>50607</v>
       </c>
     </row>
     <row r="359">
@@ -43902,7 +43902,7 @@
         </is>
       </c>
       <c r="G359" t="n">
-        <v>3650000</v>
+        <v>3951125</v>
       </c>
     </row>
     <row r="360">
@@ -43937,7 +43937,7 @@
         </is>
       </c>
       <c r="G360" t="n">
-        <v>10707450</v>
+        <v>11590815</v>
       </c>
     </row>
     <row r="361">
@@ -43972,7 +43972,7 @@
         </is>
       </c>
       <c r="G361" t="n">
-        <v>3850000</v>
+        <v>4167625</v>
       </c>
     </row>
     <row r="362">
@@ -44007,7 +44007,7 @@
         </is>
       </c>
       <c r="G362" t="n">
-        <v>3850000</v>
+        <v>4167625</v>
       </c>
     </row>
     <row r="363">
@@ -44042,7 +44042,7 @@
         </is>
       </c>
       <c r="G363" t="n">
-        <v>16990</v>
+        <v>18392</v>
       </c>
     </row>
     <row r="364">
@@ -44077,7 +44077,7 @@
         </is>
       </c>
       <c r="G364" t="n">
-        <v>739658</v>
+        <v>800680</v>
       </c>
     </row>
     <row r="365">
@@ -44112,7 +44112,7 @@
         </is>
       </c>
       <c r="G365" t="n">
-        <v>821534</v>
+        <v>889311</v>
       </c>
     </row>
     <row r="366">
@@ -44147,7 +44147,7 @@
         </is>
       </c>
       <c r="G366" t="n">
-        <v>11098225</v>
+        <v>12013829</v>
       </c>
     </row>
     <row r="367">
@@ -44182,7 +44182,7 @@
         </is>
       </c>
       <c r="G367" t="n">
-        <v>699900</v>
+        <v>757642</v>
       </c>
     </row>
     <row r="368">
@@ -44217,7 +44217,7 @@
         </is>
       </c>
       <c r="G368" t="n">
-        <v>15615</v>
+        <v>16903</v>
       </c>
     </row>
     <row r="369">
@@ -44252,7 +44252,7 @@
         </is>
       </c>
       <c r="G369" t="n">
-        <v>69296</v>
+        <v>75013</v>
       </c>
     </row>
     <row r="370">
@@ -44287,7 +44287,7 @@
         </is>
       </c>
       <c r="G370" t="n">
-        <v>137</v>
+        <v>148</v>
       </c>
     </row>
     <row r="371">
@@ -44322,7 +44322,7 @@
         </is>
       </c>
       <c r="G371" t="n">
-        <v>3250</v>
+        <v>3613</v>
       </c>
     </row>
     <row r="372">
@@ -44357,7 +44357,7 @@
         </is>
       </c>
       <c r="G372" t="n">
-        <v>3120</v>
+        <v>3312</v>
       </c>
     </row>
     <row r="373">
@@ -44392,7 +44392,7 @@
         </is>
       </c>
       <c r="G373" t="n">
-        <v>280</v>
+        <v>303</v>
       </c>
     </row>
     <row r="374">
@@ -44427,7 +44427,7 @@
         </is>
       </c>
       <c r="G374" t="n">
-        <v>3990000</v>
+        <v>4319175</v>
       </c>
     </row>
     <row r="375">
@@ -44462,7 +44462,7 @@
         </is>
       </c>
       <c r="G375" t="n">
-        <v>11832000</v>
+        <v>12808140</v>
       </c>
     </row>
     <row r="376">
@@ -44497,7 +44497,7 @@
         </is>
       </c>
       <c r="G376" t="n">
-        <v>604500</v>
+        <v>654371</v>
       </c>
     </row>
   </sheetData>
@@ -44583,7 +44583,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>70000</v>
+        <v>72891</v>
       </c>
     </row>
     <row r="3">
@@ -44618,7 +44618,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>110000</v>
+        <v>114543</v>
       </c>
     </row>
     <row r="4">
@@ -44653,7 +44653,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>4990</v>
+        <v>5196</v>
       </c>
     </row>
     <row r="5">
@@ -44688,7 +44688,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>41206879</v>
+        <v>42908723</v>
       </c>
     </row>
     <row r="6">
@@ -44723,7 +44723,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>4050000</v>
+        <v>4217265</v>
       </c>
     </row>
     <row r="7">
@@ -44758,7 +44758,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>8751547</v>
+        <v>9112986</v>
       </c>
     </row>
     <row r="8">
@@ -44793,7 +44793,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>12086000</v>
+        <v>12585152</v>
       </c>
     </row>
     <row r="9">
@@ -44828,7 +44828,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>250000</v>
+        <v>260325</v>
       </c>
     </row>
     <row r="10">
@@ -45143,7 +45143,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>70000</v>
+        <v>75775</v>
       </c>
     </row>
     <row r="19">
@@ -45178,7 +45178,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>110000</v>
+        <v>119075</v>
       </c>
     </row>
     <row r="20">
@@ -45213,7 +45213,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>4990</v>
+        <v>5402</v>
       </c>
     </row>
     <row r="21">
@@ -45248,7 +45248,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>41206879</v>
+        <v>44606447</v>
       </c>
     </row>
     <row r="22">
@@ -45283,7 +45283,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>4050000</v>
+        <v>4384125</v>
       </c>
     </row>
     <row r="23">
@@ -45318,7 +45318,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>8751547</v>
+        <v>9473550</v>
       </c>
     </row>
     <row r="24">
@@ -45353,7 +45353,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>12086000</v>
+        <v>13083095</v>
       </c>
     </row>
     <row r="25">
@@ -45388,7 +45388,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>250000</v>
+        <v>270625</v>
       </c>
     </row>
     <row r="26">
@@ -45423,7 +45423,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>70000</v>
+        <v>64218</v>
       </c>
     </row>
     <row r="27">
@@ -45458,7 +45458,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>110000</v>
+        <v>100914</v>
       </c>
     </row>
     <row r="28">
@@ -45493,7 +45493,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>4990</v>
+        <v>4578</v>
       </c>
     </row>
     <row r="29">
@@ -45528,7 +45528,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>41206879</v>
+        <v>37803191</v>
       </c>
     </row>
     <row r="30">
@@ -45563,7 +45563,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>4050000</v>
+        <v>3715470</v>
       </c>
     </row>
     <row r="31">
@@ -45598,7 +45598,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>8751547</v>
+        <v>8028669</v>
       </c>
     </row>
     <row r="32">
@@ -45633,7 +45633,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>12086000</v>
+        <v>11087696</v>
       </c>
     </row>
     <row r="33">
@@ -45668,7 +45668,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>250000</v>
+        <v>229350</v>
       </c>
     </row>
     <row r="34">
@@ -45703,7 +45703,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>70000</v>
+        <v>67109</v>
       </c>
     </row>
     <row r="35">
@@ -45738,7 +45738,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>110000</v>
+        <v>105457</v>
       </c>
     </row>
     <row r="36">
@@ -45773,7 +45773,7 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>4990</v>
+        <v>4784</v>
       </c>
     </row>
     <row r="37">
@@ -45808,7 +45808,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>41206879</v>
+        <v>39505035</v>
       </c>
     </row>
     <row r="38">
@@ -45843,7 +45843,7 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>4050000</v>
+        <v>3882735</v>
       </c>
     </row>
     <row r="39">
@@ -45878,7 +45878,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>8751547</v>
+        <v>8390108</v>
       </c>
     </row>
     <row r="40">
@@ -45913,7 +45913,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>12086000</v>
+        <v>11586848</v>
       </c>
     </row>
     <row r="41">
@@ -45948,7 +45948,7 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>250000</v>
+        <v>239675</v>
       </c>
     </row>
   </sheetData>

--- a/base_datos.xlsx
+++ b/base_datos.xlsx
@@ -1,31 +1,29 @@
 
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
-  </bookViews>
-  <sheets>
-    <sheet name="CAÑERIAS AP" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="CAÑERIAS MP" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="CAÑERIAS BP" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="SERVICIO CAÑERIAS" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="CONEXIONES" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="OBRAS CIVILES" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="NORMALIZACIONES" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="EQUIPO COMPRA DIRECTA" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="SERVICIO COMPRA DIRECTA" sheetId="9" state="visible" r:id="rId9"/>
-  </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CAÑERIAS AP'!$A$1:$G$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CAÑERIAS MP'!$A$1:$G$86</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'CAÑERIAS BP'!$A$1:$H$86</definedName>
-  </definedNames>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
-</workbook>
+<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties">
+  <Application>Microsoft Excel Compatible / Openpyxl 3.1.5</Application>
+  <AppVersion>3.1</AppVersion>
+</Properties>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
+<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <dc:creator>openpyxl</dc:creator>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-06-30T21:56:42Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-07-23T22:56:37Z</dcterms:modified>
+  <cp:lastModifiedBy>Daniel Villalobos Carrizo</cp:lastModifiedBy>
+</cp:coreProperties>
+</file>
+
+<file path=docProps\custom.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes" xmlns="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties">
+  <property name="KriptosClassAi" fmtid="{D5CDD505-2E9C-101B-9397-08002B2CF9AE}" pid="2">
+    <vt:lpwstr>1-Uso Interno</vt:lpwstr>
+  </property>
+</Properties>
+</file>
+
+<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
   <fonts count="1">
@@ -155,7 +153,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -438,7 +436,33 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+  </bookViews>
+  <sheets>
+    <sheet name="CAÑERIAS AP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="CAÑERIAS MP" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="CAÑERIAS BP" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="SERVICIO CAÑERIAS" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="CONEXIONES" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="OBRAS CIVILES" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="NORMALIZACIONES" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="EQUIPO COMPRA DIRECTA" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="SERVICIO COMPRA DIRECTA" sheetId="9" state="visible" r:id="rId9"/>
+  </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CAÑERIAS AP'!$A$1:$G$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CAÑERIAS MP'!$A$1:$G$86</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'CAÑERIAS BP'!$A$1:$H$86</definedName>
+  </definedNames>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
+</workbook>
+</file>
+
+<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2117,7 +2141,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5213,7 +5237,7 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="78" hidden="1">
@@ -5588,7 +5612,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8685,7 +8709,7 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="78" hidden="1">
@@ -9060,7 +9084,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9141,7 +9165,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>3248</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="3">
@@ -9176,7 +9200,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>16238</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="4">
@@ -10689,13 +10713,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G271"/>
+  <dimension ref="A1:G273"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="12.5703125" bestFit="1" customWidth="1" min="3" max="3"/>
@@ -10840,7 +10864,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>29769</v>
+        <v>12784</v>
       </c>
     </row>
     <row r="5">
@@ -13745,7 +13769,7 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>54125</v>
+        <v>30899</v>
       </c>
     </row>
     <row r="88">
@@ -18435,7 +18459,7 @@
         </is>
       </c>
       <c r="G221" t="n">
-        <v>45248</v>
+        <v>31586</v>
       </c>
     </row>
     <row r="222">
@@ -18715,7 +18739,7 @@
         </is>
       </c>
       <c r="G229" t="n">
-        <v>70230</v>
+        <v>64878</v>
       </c>
     </row>
     <row r="230">
@@ -20186,6 +20210,76 @@
       </c>
       <c r="G271" t="n">
         <v>38000</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>CONEXIÓN VALV CORTE 1 1/2" ALTA PRESION</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>1000241</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>CONEXIONES</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>Oficina Ventas Copiapó</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>0005</t>
+        </is>
+      </c>
+      <c r="G271">
+        <v>94425</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>MANO DE OBRA MANTENCION INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>1000274</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>CONEXIONES</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>Oficina Ventas Copiapó</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>0005</t>
+        </is>
+      </c>
+      <c r="G271">
+        <v>2500</v>
       </c>
     </row>
   </sheetData>
@@ -20193,13 +20287,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G126"/>
+  <dimension ref="A1:G127"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="14.42578125" bestFit="1" customWidth="1" min="3" max="3"/>
@@ -20414,7 +20508,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>41175</v>
+        <v>30183</v>
       </c>
     </row>
     <row r="7">
@@ -23249,7 +23343,7 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>15155</v>
+        <v>7588</v>
       </c>
     </row>
     <row r="88">
@@ -23809,7 +23903,7 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>108250</v>
+        <v>12271</v>
       </c>
     </row>
     <row r="104">
@@ -24299,7 +24393,7 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>3789</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="118">
@@ -24615,6 +24709,41 @@
       </c>
       <c r="G126" t="n">
         <v>200000</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>MANO OBRA INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>1000690</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>OBRAS CIVILES</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Oficina Ventas Copiapó</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>0005</t>
+        </is>
+      </c>
+      <c r="G126">
+        <v>20000</v>
       </c>
     </row>
   </sheetData>
@@ -24622,7 +24751,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -25858,7 +25987,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>16238</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="36">
@@ -28343,7 +28472,7 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>70362</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="107">
@@ -30618,7 +30747,7 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>129900</v>
+        <v>105000</v>
       </c>
     </row>
   </sheetData>
@@ -30626,13 +30755,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G376"/>
+  <dimension ref="A1:G377"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="46.140625" customWidth="1" min="3" max="3"/>
@@ -41522,7 +41651,7 @@
         </is>
       </c>
       <c r="G311" t="n">
-        <v>35820</v>
+        <v>29536</v>
       </c>
     </row>
     <row r="312">
@@ -42047,7 +42176,7 @@
         </is>
       </c>
       <c r="G326" t="n">
-        <v>5644</v>
+        <v>5400</v>
       </c>
     </row>
     <row r="327">
@@ -42152,7 +42281,7 @@
         </is>
       </c>
       <c r="G329" t="n">
-        <v>8738</v>
+        <v>8006</v>
       </c>
     </row>
     <row r="330">
@@ -43798,6 +43927,41 @@
       </c>
       <c r="G376" t="n">
         <v>654371</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>REGULADOR 67/684 FISHER</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>000000000000004769</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>EQUIPO COMPRA DIRECTA</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>Oficina Ventas Copiapó</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>0005</t>
+        </is>
+      </c>
+      <c r="G376">
+        <v>39579</v>
       </c>
     </row>
   </sheetData>
@@ -43805,7 +43969,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/base_datos.xlsx
+++ b/base_datos.xlsx
@@ -20247,41 +20247,6 @@
         <v>94425</v>
       </c>
     </row>
-    <row r="273">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>MANO DE OBRA MANTENCION INDUSTRIAL</t>
-        </is>
-      </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>1000274</t>
-        </is>
-      </c>
-      <c r="C271" t="inlineStr">
-        <is>
-          <t>CONEXIONES</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr">
-        <is>
-          <t>ST</t>
-        </is>
-      </c>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t>Oficina Ventas Copiapó</t>
-        </is>
-      </c>
-      <c r="F271" t="inlineStr">
-        <is>
-          <t>0005</t>
-        </is>
-      </c>
-      <c r="G271">
-        <v>2500</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/base_datos.xlsx
+++ b/base_datos.xlsx
@@ -22429,7 +22429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24182,6 +24182,146 @@
       </c>
       <c r="G50" t="n">
         <v>4800</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>DETECCION ESCAPE</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>1000046</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>SERVICIO CAÑERIAS</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Oficina Ventas San Fernando</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0110</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>VIATICO TRASLADO</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1000640</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>SERVICIO CAÑERIAS</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>KM</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Oficina Ventas San Fernando</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0110</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>MANO OBRA INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>1000690</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>SERVICIO CAÑERIAS</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Oficina Ventas San Fernando</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>0110</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>ANCLAJE Y PINTURA CAÑERIA AEREA</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>1001200</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>SERVICIO CAÑERIAS</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Oficina Ventas San Fernando</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>0110</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>3000</v>
       </c>
     </row>
   </sheetData>
@@ -24195,7 +24335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G250"/>
+  <dimension ref="A1:G267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32948,6 +33088,601 @@
       </c>
       <c r="G250" t="n">
         <v>20000</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>CONEXIÓN ANAFE INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>1000005</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>CONEXIONES</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Oficina Ventas San Fernando</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>0110</t>
+        </is>
+      </c>
+      <c r="G251" t="n">
+        <v>9744</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>CONEXIÓN FLEXIBLES 3/4"</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>1000058</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>CONEXIONES</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Oficina Ventas San Fernando</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>0110</t>
+        </is>
+      </c>
+      <c r="G252" t="n">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>GABINETE PROTECCION CALEFON</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>1000069</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>CONEXIONES</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Oficina Ventas San Fernando</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>0110</t>
+        </is>
+      </c>
+      <c r="G253" t="n">
+        <v>23750</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>CONEXIÓN HORNO INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>1000075</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>CONEXIONES</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>Oficina Ventas San Fernando</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>0110</t>
+        </is>
+      </c>
+      <c r="G254" t="n">
+        <v>320000</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>INTERCONEXION SERV. P/ 3 EST. AEREOS DE</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>1000087</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>CONEXIONES</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>Oficina Ventas San Fernando</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>0110</t>
+        </is>
+      </c>
+      <c r="G255" t="n">
+        <v>134565</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>VENTILACION CALEFONT 5"</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>1000267</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>CONEXIONES</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>Oficina Ventas San Fernando</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>0110</t>
+        </is>
+      </c>
+      <c r="G256" t="n">
+        <v>20726</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>VIATICO TRASLADO</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>1000640</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>CONEXIONES</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>KM</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>Oficina Ventas San Fernando</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>0110</t>
+        </is>
+      </c>
+      <c r="G257" t="n">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>VIATICO ALIMENTACION</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>1000642</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>CONEXIONES</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Oficina Ventas San Fernando</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>0110</t>
+        </is>
+      </c>
+      <c r="G258" t="n">
+        <v>2752</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>MANO OBRA INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>1000690</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>CONEXIONES</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>Oficina Ventas San Fernando</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>0110</t>
+        </is>
+      </c>
+      <c r="G259" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>MANIFOLD INTERCONEXION 2 S.BALON AEREOS</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>1001700</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>CONEXIONES</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Oficina Ventas San Fernando</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>0110</t>
+        </is>
+      </c>
+      <c r="G260" t="n">
+        <v>64878</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>MANIFOLD INTERCONEXION 3 S.BALON AEREOS</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>1001701</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>CONEXIONES</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Oficina Ventas San Fernando</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>0110</t>
+        </is>
+      </c>
+      <c r="G261" t="n">
+        <v>107028</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>CONEXIÓN QUEMADOR INDUSTRIAL,RED EN 3/4"</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>1000190</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>CONEXIONES</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Oficina Ventas San Fernando</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>0110</t>
+        </is>
+      </c>
+      <c r="G262" t="n">
+        <v>28597</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>CONEXIÓN HORNO DOMESTICO</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>1000074</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>CONEXIONES</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Oficina Ventas San Fernando</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>0110</t>
+        </is>
+      </c>
+      <c r="G263" t="n">
+        <v>11990</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>CONEXIÓN REGULADOR ETAPA UNICA</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>1000630</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>CONEXIONES</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Oficina Ventas San Fernando</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>0110</t>
+        </is>
+      </c>
+      <c r="G264" t="n">
+        <v>26419</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>CONEXION HORNO DOM-COM 3/4"</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>1001213</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>CONEXIONES</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>Oficina Ventas San Fernando</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>0110</t>
+        </is>
+      </c>
+      <c r="G265" t="n">
+        <v>19995</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>CONEXIÓN ESTUFA MURAL</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>1000054</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>CONEXIONES</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>Oficina Ventas San Fernando</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>0110</t>
+        </is>
+      </c>
+      <c r="G266" t="n">
+        <v>11792</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>CONEXIÓN AGUA CALEFONT</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>1000004</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>CONEXIONES</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Oficina Ventas San Fernando</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>0110</t>
+        </is>
+      </c>
+      <c r="G267" t="n">
+        <v>13480</v>
       </c>
     </row>
   </sheetData>
@@ -32961,7 +33696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G226"/>
+  <dimension ref="A1:G235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40874,6 +41609,321 @@
       </c>
       <c r="G226" t="n">
         <v>20000</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>ANCLAJE DE ESTANQUE AEREO HASTA 4000 LTS</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>1000006</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>OBRAS CIVILES</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Oficina Ventas San Fernando</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>0110</t>
+        </is>
+      </c>
+      <c r="G227" t="n">
+        <v>7588</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>BASES ESTANQUE SUPER BALON 190 KG.</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>1000013</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>OBRAS CIVILES</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Oficina Ventas San Fernando</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>0110</t>
+        </is>
+      </c>
+      <c r="G228" t="n">
+        <v>12271</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>PROTECCION METALICA PARA REGULADOR</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>OBRAS CIVILES</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Oficina Ventas San Fernando</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>0110</t>
+        </is>
+      </c>
+      <c r="G229" t="n">
+        <v>8500</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>MANO OBRA INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>1000690</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>OBRAS CIVILES</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Oficina Ventas San Fernando</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>0110</t>
+        </is>
+      </c>
+      <c r="G230" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>CELOSIA EN MURO CON TESTIGUERA</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>1000962</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>OBRAS CIVILES</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Oficina Ventas San Fernando</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>0110</t>
+        </is>
+      </c>
+      <c r="G231" t="n">
+        <v>28261</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>REJA ESTANQUE SUPERBALON 190</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>1000219</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>OBRAS CIVILES</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Oficina Ventas San Fernando</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>0110</t>
+        </is>
+      </c>
+      <c r="G232" t="n">
+        <v>200417</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>VENTILACION 5 1/2" DOBLE</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>1000265</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>OBRAS CIVILES</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Oficina Ventas San Fernando</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>0110</t>
+        </is>
+      </c>
+      <c r="G233" t="n">
+        <v>21373</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>INSTALACION CODO 45 P/ VENTILACION DE 5"</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>1000851</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>OBRAS CIVILES</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Oficina Ventas San Fernando</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>0110</t>
+        </is>
+      </c>
+      <c r="G234" t="n">
+        <v>6769</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>BASE DE CEMENTO 2 X 45 KGS.</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>1000010</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>OBRAS CIVILES</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Oficina Ventas San Fernando</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>0110</t>
+        </is>
+      </c>
+      <c r="G235" t="n">
+        <v>13000</v>
       </c>
     </row>
   </sheetData>
@@ -40887,7 +41937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G430"/>
+  <dimension ref="A1:G433"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55940,6 +56990,111 @@
       </c>
       <c r="G430" t="n">
         <v>50000</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>MANO OBRA INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>1000690</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>NORMALIZACIONES</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>Oficina Ventas San Fernando</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>0110</t>
+        </is>
+      </c>
+      <c r="G431" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>CERTIFICACION INTEGRAL COMERCIAL</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>1000819</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>NORMALIZACIONES</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>Oficina Ventas San Fernando</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>0110</t>
+        </is>
+      </c>
+      <c r="G432" t="n">
+        <v>117414</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>VISITAS REGULARI. DE INSTALACI. GRANEL</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>1001879</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>NORMALIZACIONES</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>Oficina Ventas San Fernando</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>0110</t>
+        </is>
+      </c>
+      <c r="G433" t="n">
+        <v>60000</v>
       </c>
     </row>
   </sheetData>

--- a/base_datos.xlsx
+++ b/base_datos.xlsx
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>9916</v>
+        <v>10942</v>
       </c>
     </row>
     <row r="3">
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>9916</v>
+        <v>10942</v>
       </c>
     </row>
     <row r="4">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9916</v>
+        <v>10942</v>
       </c>
     </row>
     <row r="5">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>9916</v>
+        <v>10942</v>
       </c>
     </row>
     <row r="6">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>9916</v>
+        <v>10942</v>
       </c>
     </row>
     <row r="7">
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>9916</v>
+        <v>10942</v>
       </c>
     </row>
     <row r="8">
@@ -754,7 +754,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>9916</v>
+        <v>10942</v>
       </c>
     </row>
     <row r="9">
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>9916</v>
+        <v>10942</v>
       </c>
     </row>
     <row r="10">
@@ -834,7 +834,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>9916</v>
+        <v>10942</v>
       </c>
     </row>
     <row r="11">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>9916</v>
+        <v>10942</v>
       </c>
     </row>
     <row r="12">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>9916</v>
+        <v>10942</v>
       </c>
     </row>
     <row r="13">
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>9916</v>
+        <v>10942</v>
       </c>
     </row>
     <row r="14">
@@ -994,7 +994,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>9916</v>
+        <v>10942</v>
       </c>
     </row>
     <row r="15">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>9557</v>
+        <v>10546</v>
       </c>
     </row>
     <row r="16">
@@ -1074,7 +1074,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>9557</v>
+        <v>10546</v>
       </c>
     </row>
     <row r="17">
@@ -1114,7 +1114,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>9557</v>
+        <v>10546</v>
       </c>
     </row>
     <row r="18">
@@ -1154,7 +1154,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>9557</v>
+        <v>10546</v>
       </c>
     </row>
     <row r="19">
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>9557</v>
+        <v>10546</v>
       </c>
     </row>
     <row r="20">
@@ -1234,7 +1234,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>9557</v>
+        <v>10546</v>
       </c>
     </row>
     <row r="21">
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>9557</v>
+        <v>10546</v>
       </c>
     </row>
     <row r="22">
@@ -1314,7 +1314,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>9557</v>
+        <v>10546</v>
       </c>
     </row>
     <row r="23">
@@ -1354,7 +1354,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>9557</v>
+        <v>10546</v>
       </c>
     </row>
     <row r="24">
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>9557</v>
+        <v>10546</v>
       </c>
     </row>
     <row r="25">
@@ -1434,7 +1434,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>9557</v>
+        <v>10546</v>
       </c>
     </row>
     <row r="26">
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>9557</v>
+        <v>10546</v>
       </c>
     </row>
     <row r="27">
@@ -1514,7 +1514,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>9557</v>
+        <v>10546</v>
       </c>
     </row>
     <row r="28">
@@ -1554,7 +1554,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>9175</v>
+        <v>10125</v>
       </c>
     </row>
     <row r="29">
@@ -1594,7 +1594,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>9175</v>
+        <v>10125</v>
       </c>
     </row>
     <row r="30">
@@ -1634,7 +1634,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>9175</v>
+        <v>10125</v>
       </c>
     </row>
     <row r="31">
@@ -1674,7 +1674,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>9175</v>
+        <v>10125</v>
       </c>
     </row>
     <row r="32">
@@ -1714,7 +1714,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>9175</v>
+        <v>10125</v>
       </c>
     </row>
     <row r="33">
@@ -1754,7 +1754,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>9175</v>
+        <v>10125</v>
       </c>
     </row>
     <row r="34">
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>9175</v>
+        <v>10125</v>
       </c>
     </row>
     <row r="35">
@@ -1834,7 +1834,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>9175</v>
+        <v>10125</v>
       </c>
     </row>
     <row r="36">
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>9175</v>
+        <v>10125</v>
       </c>
     </row>
     <row r="37">
@@ -1914,7 +1914,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>9175</v>
+        <v>10125</v>
       </c>
     </row>
     <row r="38">
@@ -1954,7 +1954,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>9175</v>
+        <v>10125</v>
       </c>
     </row>
     <row r="39">
@@ -1994,7 +1994,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>9175</v>
+        <v>10125</v>
       </c>
     </row>
     <row r="40">
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>9175</v>
+        <v>10125</v>
       </c>
     </row>
     <row r="41">
@@ -2074,7 +2074,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="42">
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="43">
@@ -2154,7 +2154,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="44">
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="45">
@@ -2234,7 +2234,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="46">
@@ -2274,7 +2274,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="47">
@@ -2314,7 +2314,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="48">
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="49">
@@ -2394,7 +2394,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="50">
@@ -2434,7 +2434,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="51">
@@ -2474,7 +2474,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="52">
@@ -2514,7 +2514,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="53">
@@ -2554,7 +2554,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="54">
@@ -3634,7 +3634,7 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="81">
@@ -3674,7 +3674,7 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="82">
@@ -3714,7 +3714,7 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="83">
@@ -3754,7 +3754,7 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="84">
@@ -3794,7 +3794,7 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="85">
@@ -3834,7 +3834,7 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="86">
@@ -3874,7 +3874,7 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="87">
@@ -3914,7 +3914,7 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="88">
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="89">
@@ -3994,7 +3994,7 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="90">
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="91">
@@ -4074,7 +4074,7 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="92">
@@ -4114,7 +4114,7 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="93">
@@ -4154,7 +4154,7 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="94">
@@ -4194,7 +4194,7 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="95">
@@ -4234,7 +4234,7 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="96">
@@ -4274,7 +4274,7 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="97">
@@ -4314,7 +4314,7 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="98">
@@ -4354,7 +4354,7 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="99">
@@ -4394,7 +4394,7 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="100">
@@ -4434,7 +4434,7 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="101">
@@ -4474,7 +4474,7 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="102">
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="103">
@@ -4554,7 +4554,7 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="104">
@@ -4594,7 +4594,7 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="105">
@@ -4634,7 +4634,7 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
   </sheetData>
@@ -8370,7 +8370,7 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>9916</v>
+        <v>10942</v>
       </c>
     </row>
     <row r="94">
@@ -8410,7 +8410,7 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>9916</v>
+        <v>10942</v>
       </c>
     </row>
     <row r="95">
@@ -8450,7 +8450,7 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>9916</v>
+        <v>10942</v>
       </c>
     </row>
     <row r="96">
@@ -8490,7 +8490,7 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>9916</v>
+        <v>10942</v>
       </c>
     </row>
     <row r="97">
@@ -8570,7 +8570,7 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>9916</v>
+        <v>10942</v>
       </c>
     </row>
     <row r="99">
@@ -8610,7 +8610,7 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>9916</v>
+        <v>10942</v>
       </c>
     </row>
     <row r="100">
@@ -8650,7 +8650,7 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>9916</v>
+        <v>10942</v>
       </c>
     </row>
     <row r="101">
@@ -8690,7 +8690,7 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>9916</v>
+        <v>10942</v>
       </c>
     </row>
     <row r="102">
@@ -8730,7 +8730,7 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>9916</v>
+        <v>10942</v>
       </c>
     </row>
     <row r="103">
@@ -8770,7 +8770,7 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>9916</v>
+        <v>10942</v>
       </c>
     </row>
     <row r="104">
@@ -8810,7 +8810,7 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>9916</v>
+        <v>10942</v>
       </c>
     </row>
     <row r="105">
@@ -8850,7 +8850,7 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>9916</v>
+        <v>10942</v>
       </c>
     </row>
     <row r="106">
@@ -8890,7 +8890,7 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>9557</v>
+        <v>10546</v>
       </c>
     </row>
     <row r="107">
@@ -8930,7 +8930,7 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>9557</v>
+        <v>10546</v>
       </c>
     </row>
     <row r="108">
@@ -8970,7 +8970,7 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>9557</v>
+        <v>10546</v>
       </c>
     </row>
     <row r="109">
@@ -9010,7 +9010,7 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>9557</v>
+        <v>10546</v>
       </c>
     </row>
     <row r="110">
@@ -9090,7 +9090,7 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>9557</v>
+        <v>10546</v>
       </c>
     </row>
     <row r="112">
@@ -9130,7 +9130,7 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>9557</v>
+        <v>10546</v>
       </c>
     </row>
     <row r="113">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>9557</v>
+        <v>10546</v>
       </c>
     </row>
     <row r="114">
@@ -9210,7 +9210,7 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>9557</v>
+        <v>10546</v>
       </c>
     </row>
     <row r="115">
@@ -9250,7 +9250,7 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>9557</v>
+        <v>10546</v>
       </c>
     </row>
     <row r="116">
@@ -9290,7 +9290,7 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>9557</v>
+        <v>10546</v>
       </c>
     </row>
     <row r="117">
@@ -9330,7 +9330,7 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>9557</v>
+        <v>10546</v>
       </c>
     </row>
     <row r="118">
@@ -9370,7 +9370,7 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>9557</v>
+        <v>10546</v>
       </c>
     </row>
     <row r="119">
@@ -9410,7 +9410,7 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>9175</v>
+        <v>10125</v>
       </c>
     </row>
     <row r="120">
@@ -9450,7 +9450,7 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>9175</v>
+        <v>10125</v>
       </c>
     </row>
     <row r="121">
@@ -9490,7 +9490,7 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>9175</v>
+        <v>10125</v>
       </c>
     </row>
     <row r="122">
@@ -9530,7 +9530,7 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>9175</v>
+        <v>10125</v>
       </c>
     </row>
     <row r="123">
@@ -9610,7 +9610,7 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>9175</v>
+        <v>10125</v>
       </c>
     </row>
     <row r="125">
@@ -9650,7 +9650,7 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>9175</v>
+        <v>10125</v>
       </c>
     </row>
     <row r="126">
@@ -9690,7 +9690,7 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>9175</v>
+        <v>10125</v>
       </c>
     </row>
     <row r="127">
@@ -9730,7 +9730,7 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>9175</v>
+        <v>10125</v>
       </c>
     </row>
     <row r="128">
@@ -9770,7 +9770,7 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>9175</v>
+        <v>10125</v>
       </c>
     </row>
     <row r="129">
@@ -9810,7 +9810,7 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>9175</v>
+        <v>10125</v>
       </c>
     </row>
     <row r="130">
@@ -9850,7 +9850,7 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>9175</v>
+        <v>10125</v>
       </c>
     </row>
     <row r="131">
@@ -9890,7 +9890,7 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>9175</v>
+        <v>10125</v>
       </c>
     </row>
     <row r="132">
@@ -9930,7 +9930,7 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="133">
@@ -9970,7 +9970,7 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="134">
@@ -10010,7 +10010,7 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="135">
@@ -10050,7 +10050,7 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="136">
@@ -10130,7 +10130,7 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="138">
@@ -10170,7 +10170,7 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="139">
@@ -10210,7 +10210,7 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="140">
@@ -10250,7 +10250,7 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="141">
@@ -10290,7 +10290,7 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="142">
@@ -10330,7 +10330,7 @@
         </is>
       </c>
       <c r="H142" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="143">
@@ -10370,7 +10370,7 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="144">
@@ -10410,7 +10410,7 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="145">
@@ -11490,7 +11490,7 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>11715</v>
+        <v>12928</v>
       </c>
     </row>
     <row r="172">
@@ -11530,7 +11530,7 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>11715</v>
+        <v>12928</v>
       </c>
     </row>
     <row r="173">
@@ -11570,7 +11570,7 @@
         </is>
       </c>
       <c r="H173" t="n">
-        <v>11715</v>
+        <v>12928</v>
       </c>
     </row>
     <row r="174">
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="H174" t="n">
-        <v>11715</v>
+        <v>12928</v>
       </c>
     </row>
     <row r="175">
@@ -11650,7 +11650,7 @@
         </is>
       </c>
       <c r="H175" t="n">
-        <v>11715</v>
+        <v>12928</v>
       </c>
     </row>
     <row r="176">
@@ -11690,7 +11690,7 @@
         </is>
       </c>
       <c r="H176" t="n">
-        <v>11715</v>
+        <v>12928</v>
       </c>
     </row>
     <row r="177">
@@ -11730,7 +11730,7 @@
         </is>
       </c>
       <c r="H177" t="n">
-        <v>11715</v>
+        <v>12928</v>
       </c>
     </row>
     <row r="178">
@@ -11770,7 +11770,7 @@
         </is>
       </c>
       <c r="H178" t="n">
-        <v>11715</v>
+        <v>12928</v>
       </c>
     </row>
     <row r="179">
@@ -11810,7 +11810,7 @@
         </is>
       </c>
       <c r="H179" t="n">
-        <v>11715</v>
+        <v>12928</v>
       </c>
     </row>
     <row r="180">
@@ -11850,7 +11850,7 @@
         </is>
       </c>
       <c r="H180" t="n">
-        <v>11715</v>
+        <v>12928</v>
       </c>
     </row>
     <row r="181">
@@ -11890,7 +11890,7 @@
         </is>
       </c>
       <c r="H181" t="n">
-        <v>11715</v>
+        <v>12928</v>
       </c>
     </row>
     <row r="182">
@@ -11930,7 +11930,7 @@
         </is>
       </c>
       <c r="H182" t="n">
-        <v>11715</v>
+        <v>12928</v>
       </c>
     </row>
     <row r="183">
@@ -11970,7 +11970,7 @@
         </is>
       </c>
       <c r="H183" t="n">
-        <v>11715</v>
+        <v>12928</v>
       </c>
     </row>
     <row r="184">
@@ -12010,7 +12010,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="185">
@@ -12050,7 +12050,7 @@
         </is>
       </c>
       <c r="H185" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="186">
@@ -12090,7 +12090,7 @@
         </is>
       </c>
       <c r="H186" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="187">
@@ -12130,7 +12130,7 @@
         </is>
       </c>
       <c r="H187" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="188">
@@ -12210,7 +12210,7 @@
         </is>
       </c>
       <c r="H189" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="190">
@@ -12250,7 +12250,7 @@
         </is>
       </c>
       <c r="H190" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="191">
@@ -12290,7 +12290,7 @@
         </is>
       </c>
       <c r="H191" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="192">
@@ -12330,7 +12330,7 @@
         </is>
       </c>
       <c r="H192" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="193">
@@ -12370,7 +12370,7 @@
         </is>
       </c>
       <c r="H193" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="194">
@@ -12410,7 +12410,7 @@
         </is>
       </c>
       <c r="H194" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="195">
@@ -12450,7 +12450,7 @@
         </is>
       </c>
       <c r="H195" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="196">
@@ -12490,7 +12490,7 @@
         </is>
       </c>
       <c r="H196" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="197">
@@ -12530,7 +12530,7 @@
         </is>
       </c>
       <c r="H197" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="198">
@@ -12570,7 +12570,7 @@
         </is>
       </c>
       <c r="H198" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="199">
@@ -12610,7 +12610,7 @@
         </is>
       </c>
       <c r="H199" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="200">
@@ -12650,7 +12650,7 @@
         </is>
       </c>
       <c r="H200" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="201">
@@ -12730,7 +12730,7 @@
         </is>
       </c>
       <c r="H202" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="203">
@@ -12770,7 +12770,7 @@
         </is>
       </c>
       <c r="H203" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="204">
@@ -12810,7 +12810,7 @@
         </is>
       </c>
       <c r="H204" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="205">
@@ -12850,7 +12850,7 @@
         </is>
       </c>
       <c r="H205" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="206">
@@ -12890,7 +12890,7 @@
         </is>
       </c>
       <c r="H206" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="207">
@@ -12930,7 +12930,7 @@
         </is>
       </c>
       <c r="H207" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="208">
@@ -12970,7 +12970,7 @@
         </is>
       </c>
       <c r="H208" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="209">
@@ -13010,7 +13010,7 @@
         </is>
       </c>
       <c r="H209" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="210">
@@ -17266,7 +17266,7 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>9916</v>
+        <v>10942</v>
       </c>
     </row>
     <row r="94">
@@ -17306,7 +17306,7 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>9916</v>
+        <v>10942</v>
       </c>
     </row>
     <row r="95">
@@ -17346,7 +17346,7 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>9916</v>
+        <v>10942</v>
       </c>
     </row>
     <row r="96">
@@ -17386,7 +17386,7 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>9916</v>
+        <v>10942</v>
       </c>
     </row>
     <row r="97">
@@ -17466,7 +17466,7 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>9916</v>
+        <v>10942</v>
       </c>
     </row>
     <row r="99">
@@ -17506,7 +17506,7 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>9916</v>
+        <v>10942</v>
       </c>
     </row>
     <row r="100">
@@ -17546,7 +17546,7 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>9916</v>
+        <v>10942</v>
       </c>
     </row>
     <row r="101">
@@ -17586,7 +17586,7 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>9916</v>
+        <v>10942</v>
       </c>
     </row>
     <row r="102">
@@ -17626,7 +17626,7 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>9916</v>
+        <v>10942</v>
       </c>
     </row>
     <row r="103">
@@ -17666,7 +17666,7 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>9916</v>
+        <v>10942</v>
       </c>
     </row>
     <row r="104">
@@ -17706,7 +17706,7 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>9916</v>
+        <v>10942</v>
       </c>
     </row>
     <row r="105">
@@ -17746,7 +17746,7 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>9916</v>
+        <v>10942</v>
       </c>
     </row>
     <row r="106">
@@ -17786,7 +17786,7 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>9557</v>
+        <v>10546</v>
       </c>
     </row>
     <row r="107">
@@ -17826,7 +17826,7 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>9557</v>
+        <v>10546</v>
       </c>
     </row>
     <row r="108">
@@ -17866,7 +17866,7 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>9557</v>
+        <v>10546</v>
       </c>
     </row>
     <row r="109">
@@ -17906,7 +17906,7 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>9557</v>
+        <v>10546</v>
       </c>
     </row>
     <row r="110">
@@ -17986,7 +17986,7 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>9557</v>
+        <v>10546</v>
       </c>
     </row>
     <row r="112">
@@ -18026,7 +18026,7 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>9557</v>
+        <v>10546</v>
       </c>
     </row>
     <row r="113">
@@ -18066,7 +18066,7 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>9557</v>
+        <v>10546</v>
       </c>
     </row>
     <row r="114">
@@ -18106,7 +18106,7 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>9557</v>
+        <v>10546</v>
       </c>
     </row>
     <row r="115">
@@ -18146,7 +18146,7 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>9557</v>
+        <v>10546</v>
       </c>
     </row>
     <row r="116">
@@ -18186,7 +18186,7 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>9557</v>
+        <v>10546</v>
       </c>
     </row>
     <row r="117">
@@ -18226,7 +18226,7 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>9557</v>
+        <v>10546</v>
       </c>
     </row>
     <row r="118">
@@ -18266,7 +18266,7 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>9557</v>
+        <v>10546</v>
       </c>
     </row>
     <row r="119">
@@ -18306,7 +18306,7 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>9175</v>
+        <v>10125</v>
       </c>
     </row>
     <row r="120">
@@ -18346,7 +18346,7 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>9175</v>
+        <v>10125</v>
       </c>
     </row>
     <row r="121">
@@ -18386,7 +18386,7 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>9175</v>
+        <v>10125</v>
       </c>
     </row>
     <row r="122">
@@ -18426,7 +18426,7 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>9175</v>
+        <v>10125</v>
       </c>
     </row>
     <row r="123">
@@ -18506,7 +18506,7 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>9175</v>
+        <v>10125</v>
       </c>
     </row>
     <row r="125">
@@ -18546,7 +18546,7 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>9175</v>
+        <v>10125</v>
       </c>
     </row>
     <row r="126">
@@ -18586,7 +18586,7 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>9175</v>
+        <v>10125</v>
       </c>
     </row>
     <row r="127">
@@ -18626,7 +18626,7 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>9175</v>
+        <v>10125</v>
       </c>
     </row>
     <row r="128">
@@ -18666,7 +18666,7 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>9175</v>
+        <v>10125</v>
       </c>
     </row>
     <row r="129">
@@ -18706,7 +18706,7 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>9175</v>
+        <v>10125</v>
       </c>
     </row>
     <row r="130">
@@ -18746,7 +18746,7 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>9175</v>
+        <v>10125</v>
       </c>
     </row>
     <row r="131">
@@ -18786,7 +18786,7 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>9175</v>
+        <v>10125</v>
       </c>
     </row>
     <row r="132">
@@ -18826,7 +18826,7 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="133">
@@ -18866,7 +18866,7 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="134">
@@ -18906,7 +18906,7 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="135">
@@ -18946,7 +18946,7 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="136">
@@ -19026,7 +19026,7 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="138">
@@ -19066,7 +19066,7 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="139">
@@ -19106,7 +19106,7 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="140">
@@ -19146,7 +19146,7 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="141">
@@ -19186,7 +19186,7 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="142">
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="H142" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="143">
@@ -19266,7 +19266,7 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="144">
@@ -19306,7 +19306,7 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="145">
@@ -20386,7 +20386,7 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>11715</v>
+        <v>12928</v>
       </c>
     </row>
     <row r="172">
@@ -20426,7 +20426,7 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>11715</v>
+        <v>12928</v>
       </c>
     </row>
     <row r="173">
@@ -20466,7 +20466,7 @@
         </is>
       </c>
       <c r="H173" t="n">
-        <v>11715</v>
+        <v>12928</v>
       </c>
     </row>
     <row r="174">
@@ -20506,7 +20506,7 @@
         </is>
       </c>
       <c r="H174" t="n">
-        <v>11715</v>
+        <v>12928</v>
       </c>
     </row>
     <row r="175">
@@ -20546,7 +20546,7 @@
         </is>
       </c>
       <c r="H175" t="n">
-        <v>11715</v>
+        <v>12928</v>
       </c>
     </row>
     <row r="176">
@@ -20586,7 +20586,7 @@
         </is>
       </c>
       <c r="H176" t="n">
-        <v>11715</v>
+        <v>12928</v>
       </c>
     </row>
     <row r="177">
@@ -20626,7 +20626,7 @@
         </is>
       </c>
       <c r="H177" t="n">
-        <v>11715</v>
+        <v>12928</v>
       </c>
     </row>
     <row r="178">
@@ -20666,7 +20666,7 @@
         </is>
       </c>
       <c r="H178" t="n">
-        <v>11715</v>
+        <v>12928</v>
       </c>
     </row>
     <row r="179">
@@ -20706,7 +20706,7 @@
         </is>
       </c>
       <c r="H179" t="n">
-        <v>11715</v>
+        <v>12928</v>
       </c>
     </row>
     <row r="180">
@@ -20746,7 +20746,7 @@
         </is>
       </c>
       <c r="H180" t="n">
-        <v>11715</v>
+        <v>12928</v>
       </c>
     </row>
     <row r="181">
@@ -20786,7 +20786,7 @@
         </is>
       </c>
       <c r="H181" t="n">
-        <v>11715</v>
+        <v>12928</v>
       </c>
     </row>
     <row r="182">
@@ -20826,7 +20826,7 @@
         </is>
       </c>
       <c r="H182" t="n">
-        <v>11715</v>
+        <v>12928</v>
       </c>
     </row>
     <row r="183">
@@ -20866,7 +20866,7 @@
         </is>
       </c>
       <c r="H183" t="n">
-        <v>11715</v>
+        <v>12928</v>
       </c>
     </row>
     <row r="184">
@@ -20906,7 +20906,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="185">
@@ -20946,7 +20946,7 @@
         </is>
       </c>
       <c r="H185" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="186">
@@ -20986,7 +20986,7 @@
         </is>
       </c>
       <c r="H186" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="187">
@@ -21026,7 +21026,7 @@
         </is>
       </c>
       <c r="H187" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="188">
@@ -21106,7 +21106,7 @@
         </is>
       </c>
       <c r="H189" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="190">
@@ -21146,7 +21146,7 @@
         </is>
       </c>
       <c r="H190" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="191">
@@ -21186,7 +21186,7 @@
         </is>
       </c>
       <c r="H191" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="192">
@@ -21226,7 +21226,7 @@
         </is>
       </c>
       <c r="H192" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="193">
@@ -21266,7 +21266,7 @@
         </is>
       </c>
       <c r="H193" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="194">
@@ -21306,7 +21306,7 @@
         </is>
       </c>
       <c r="H194" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="195">
@@ -21346,7 +21346,7 @@
         </is>
       </c>
       <c r="H195" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="196">
@@ -21386,7 +21386,7 @@
         </is>
       </c>
       <c r="H196" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="197">
@@ -21426,7 +21426,7 @@
         </is>
       </c>
       <c r="H197" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="198">
@@ -21466,7 +21466,7 @@
         </is>
       </c>
       <c r="H198" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="199">
@@ -21506,7 +21506,7 @@
         </is>
       </c>
       <c r="H199" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="200">
@@ -21546,7 +21546,7 @@
         </is>
       </c>
       <c r="H200" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="201">
@@ -21626,7 +21626,7 @@
         </is>
       </c>
       <c r="H202" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="203">
@@ -21666,7 +21666,7 @@
         </is>
       </c>
       <c r="H203" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="204">
@@ -21706,7 +21706,7 @@
         </is>
       </c>
       <c r="H204" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="205">
@@ -21746,7 +21746,7 @@
         </is>
       </c>
       <c r="H205" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="206">
@@ -21786,7 +21786,7 @@
         </is>
       </c>
       <c r="H206" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="207">
@@ -21826,7 +21826,7 @@
         </is>
       </c>
       <c r="H207" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="208">
@@ -21866,7 +21866,7 @@
         </is>
       </c>
       <c r="H208" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="209">
@@ -21906,7 +21906,7 @@
         </is>
       </c>
       <c r="H209" t="n">
-        <v>8502</v>
+        <v>9382</v>
       </c>
     </row>
     <row r="210">
